--- a/Оценка_360_руководители_проектов.xlsx
+++ b/Оценка_360_руководители_проектов.xlsx
@@ -39,12 +39,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="001F4E79"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="009C0006"/>
       <sz val="11"/>
     </font>
     <font>
@@ -73,7 +73,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -113,6 +113,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
       </patternFill>
     </fill>
   </fills>
@@ -193,7 +198,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -594,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B30"/>
+  <dimension ref="B1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -611,159 +616,166 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ: все 7 блоков заполнены ДЕМОНСТРАЦИОННЫМИ данными (пример, не реальные оценки). Файл показывает, как выглядит завершённый отчёт. Для реального 360 замените оценки на реальные оценки опрашиваемых — «Сводка» и «Итоги» пересчитаются автоматически.</t>
+          <t>Состав: 6 руководителей проектов — Кущенко Д. А., Горбунова А. М., Бутым Б. С., Маслаков А. В., Яковлев А. В., Неробеева А. Э..</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>ВНИМАНИЕ: все 6 блоков заполнены ДЕМОНСТРАЦИОННЫМИ оценками (пример, не реальные результаты). Файл показывает, как выглядит завершённый отчёт. Для реального 360 замените оценки на реальные оценки опрашиваемых — «Сводка» и «Итоги» пересчитаются автоматически.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>Что такое оценка 360°. Руководитель проекта оценивается по ряду компетенций несколькими группами: его непосредственный руководитель, коллеги, подчинённые, внутренние клиенты (предприятия-участники, ФЦК, смежные подразделения), плюс самооценка. Это даёт картину «со всех сторон» и показывает слепые зоны — где человек оценивает себя выше, чем его видят окружающие.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>ШКАЛА ОЦЕНИВАНИЯ (для всех компетенций):</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>1 — Не соответствует: поведение не наблюдается, компетенция не проявляется</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>2 — Частично соответствует: проявления единичные, нестабильные</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3 — Соответствует: устойчивое поведение, соответствует требованиям</t>
+          <t>1 — Не соответствует: поведение не наблюдается, компетенция не проявляется</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4 — Высокий уровень: устойчиво превышает требования, пример для коллег</t>
+          <t>2 — Частично соответствует: проявления единичные, нестабильные</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
+          <t>3 — Соответствует: устойчивое поведение, соответствует требованиям</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>4 — Высокий уровень: устойчиво превышает требования, пример для коллег</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
           <t>5 — Выдающийся: лучший в организации, менторит и обучает других</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>ШАГИ ПРОВЕДЕНИЯ:</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>1. Подготовьте список опрашиваемых для каждого из 7 руководителей. Рекомендуемый состав: 1 непосредственный руководитель; 3–5 коллег (соседние руководители проектов); 3–5 подчинённых; 1–2 внутренних клиента (предприятия-участники, куратор/ФЦК). Самооценку руководитель заполняет сам. Всего на человека — 8–15 респондентов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>2. Проведите короткий инструктаж респондентов: цель оценки — развитие (не депремирование), шкала 1–5, конфиденциальность (результаты отдельных людей никому не показываются), срок — 2–3 недели.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>3. Сбор оценок. Либо каждый респондент заполняет в листе «Оценки» только СВОЙ столбец в блоке того руководителя, которого он оценивает (файл по очереди передаётся), либо оценки собираются онлайн-формой, а вы вносите их в лист «Оценки». Целые числа от 1 до 5 (есть проверка ввода).</t>
+          <t>1. Подготовьте список опрашиваемых для каждого из 6 руководителей. Рекомендуемый состав: 1 непосредственный руководитель; 3–5 коллег (соседние руководители проектов); 3–5 подчинённых; 1–2 внутренних клиента (предприятия-участники, куратор/ФЦК). Самооценку руководитель заполняет сам. Всего на человека — 8–15 респондентов.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>4. Лист «Сводка» считается автоматически: средние по группам, общий средний балл «Другие» и разрыв «себя vs. другие» по каждой компетенции. Сигналы: красный разрыв ≥ 0,5 — руководитель переоценивает себя; оранжевый средний балл «Другие» &lt; 3 — компетенция ниже требуемого уровня.</t>
+          <t>2. Проведите короткий инструктаж респондентов: цель оценки — развитие (не депремирование), шкала 1–5, конфиденциальность (результаты отдельных людей никому не показываются), срок — 2–3 недели.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>5. Лист «Итоги» — готовый отчёт по каждому руководителю: общий балл «Другие», разрыв, средние по 4 группам «Действий», сильные стороны, зоны развития и слепые зоны (считается автоматически).</t>
+          <t>3. Сбор оценок. Либо каждый респондент заполняет в листе «Оценки» только СВОЙ столбец в блоке того руководителя, которого он оценивает (файл по очереди передаётся), либо оценки собираются онлайн-формой, а вы вносите их в лист «Оценки». Целые числа от 1 до 5 (есть проверка ввода).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>4. Лист «Сводка» считается автоматически: средние по группам, общий средний балл «Другие» и разрыв «себя vs. другие» по каждой компетенции. Сигналы: красный разрыв ≥ 0,5 — руководитель переоценивает себя; оранжевый средний балл «Другие» &lt; 3 — компетенция ниже требуемого уровня.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>5. Лист «Итоги» — готовый отчёт по каждому руководителю: общий балл «Другие», разрыв, средние по 4 группам «Действий», сильные стороны, зоны развития и слепые зоны (считается автоматически).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
           <t>6. Проведите личную встречу с каждым руководителем (20–30 минут): покажите сводку (только групповые средние, без имён), обсудите 2–3 сильные стороны и 2–3 зоны развития, согласуйте план развития (лист «План развития», формат — по приложению № 6 МР).</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>ПРАВИЛА КОНФИДЕНЦИАЛЬНОСТИ:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>• Опасываемый видит только средние по группам и общий результат — не оценки конкретных людей.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>• Лист «Оценки» (сырые данные) хранит и видит только организатор оценки (вы).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>• В группе должно быть не менее 2 респондентов, иначе средний балл группы нерепрезентативен — дополните группу или не показывайте её. Столбцы заготовлены на 3 коллег и 3 подчинённых; если людей меньше — оставьте пустые ячейки, формулы посчитают по заполненным.</t>
+          <t>• Опасываемый видит только средние по группам и общий результат — не оценки конкретных людей.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
+          <t>• Лист «Оценки» (сырые данные) хранит и видит только организатор оценки (вы).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>• В группе должно быть не менее 2 респондентов, иначе средний балл группы нерепрезентативен — дополните группу или не показывайте её. Столбцы заготовлены на 3 коллег и 3 подчинённых; если людей меньше — оставьте пустые ячейки, формулы посчитают по заполненным.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>• Оценки используются для развития (coaching, обучение, план развития), а не для депремирования — иначе респонденты будут оценивать «для галочки».</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>ИСТОЧНИК КОМПЕТЕНЦИЙ:</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>• 37 компетенций — модель профессиональных компетенций сотрудников РЦК (приложение № 3 МР-02-2025 «Организация работы региональных центров компетенций в сфере производительности труда в субъектах РФ», ред. 1, утв. ФЦК 28.01.2025), 4 группы «Действий». Ссылки на пункты МР — на листе «Компетенции».</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>• Формат плана развития и шкала уровней (0–3, шаг 0,5) — приложение № 6 МР-02-2025 «Организация работы региональных центров компетенций в сфере производительности труда в субъектах РФ», ред. 1, утв. ФЦК 28.01.2025. Пункт 10.4 МР: матрица компетенций и планы развития сотрудников размещаются в инфоцентре РЦК.</t>
         </is>
@@ -1580,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K274"/>
+  <dimension ref="A1:K235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1663,7 +1675,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3051,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4427,7 @@
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="18" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
     </row>
@@ -5791,7 +5803,7 @@
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="18" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7179,7 @@
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="18" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8555,7 @@
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="18" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
     </row>
@@ -9916,1387 +9928,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" ht="20" customHeight="1">
-      <c r="A237" s="18" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B238" s="16" t="inlineStr">
-        <is>
-          <t>Проведение оценки на соответствие предприятия обязательным критериям</t>
-        </is>
-      </c>
-      <c r="C238" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D238" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E238" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F238" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="G238" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H238" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="I238" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J238" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K238" s="17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B239" s="16" t="inlineStr">
-        <is>
-          <t>Проведение оценки готовности руководства предприятия к участию в проекте (интервью)</t>
-        </is>
-      </c>
-      <c r="C239" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D239" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E239" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F239" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="G239" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H239" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I239" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="J239" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K239" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B240" s="16" t="inlineStr">
-        <is>
-          <t>Проведение визуальной оценки производственного процесса на предприятии (визит на площадку)</t>
-        </is>
-      </c>
-      <c r="C240" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D240" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E240" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F240" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G240" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H240" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I240" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J240" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K240" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B241" s="16" t="inlineStr">
-        <is>
-          <t>Вовлечение руководства предприятий в федеральный проект</t>
-        </is>
-      </c>
-      <c r="C241" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D241" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E241" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F241" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G241" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H241" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I241" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J241" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K241" s="17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B242" s="16" t="inlineStr">
-        <is>
-          <t>Подписание соглашения о сотрудничестве между РЦК и предприятием</t>
-        </is>
-      </c>
-      <c r="C242" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D242" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E242" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F242" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G242" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H242" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I242" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J242" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K242" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B243" s="16" t="inlineStr">
-        <is>
-          <t>Реализация организационных вех программы</t>
-        </is>
-      </c>
-      <c r="C243" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D243" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E243" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F243" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G243" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H243" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I243" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J243" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K243" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B244" s="16" t="inlineStr">
-        <is>
-          <t>Формирование проектного офиса</t>
-        </is>
-      </c>
-      <c r="C244" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D244" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E244" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F244" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G244" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H244" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I244" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J244" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K244" s="17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B245" s="16" t="inlineStr">
-        <is>
-          <t>Определение перечня вовлеченных лиц и рамок проекта; создание рабочей группы для работы с пилотным потоком</t>
-        </is>
-      </c>
-      <c r="C245" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D245" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E245" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F245" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G245" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H245" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I245" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J245" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K245" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B246" s="16" t="inlineStr">
-        <is>
-          <t>Выявление степени готовности предприятия к изменениям</t>
-        </is>
-      </c>
-      <c r="C246" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D246" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E246" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F246" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G246" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H246" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I246" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J246" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K246" s="17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B247" s="16" t="inlineStr">
-        <is>
-          <t>Составление плана ключевых событий</t>
-        </is>
-      </c>
-      <c r="C247" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D247" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E247" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F247" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G247" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H247" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I247" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J247" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K247" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B248" s="16" t="inlineStr">
-        <is>
-          <t>Разработка и корректировка плана мероприятий (основные этапы, сроки, ответственные) по достижению целевого состояния</t>
-        </is>
-      </c>
-      <c r="C248" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D248" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E248" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F248" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G248" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H248" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I248" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="J248" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K248" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B249" s="16" t="inlineStr">
-        <is>
-          <t>Проведение анализа показателей проектов повышения производительности труда</t>
-        </is>
-      </c>
-      <c r="C249" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D249" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E249" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F249" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G249" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H249" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I249" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J249" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K249" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B250" s="16" t="inlineStr">
-        <is>
-          <t>Создание карточки проекта</t>
-        </is>
-      </c>
-      <c r="C250" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D250" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E250" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F250" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G250" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H250" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I250" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J250" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K250" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B251" s="16" t="inlineStr">
-        <is>
-          <t>Создание информационного центра проекта</t>
-        </is>
-      </c>
-      <c r="C251" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D251" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E251" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F251" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G251" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H251" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I251" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J251" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K251" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B252" s="16" t="inlineStr">
-        <is>
-          <t>Создание эталонного участка</t>
-        </is>
-      </c>
-      <c r="C252" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D252" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E252" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F252" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G252" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H252" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I252" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J252" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K252" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B253" s="16" t="inlineStr">
-        <is>
-          <t>Проведение оценки уровня развития производственной системы предприятия</t>
-        </is>
-      </c>
-      <c r="C253" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D253" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E253" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F253" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G253" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H253" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I253" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J253" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K253" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B254" s="16" t="inlineStr">
-        <is>
-          <t>Внедрение информационных центров</t>
-        </is>
-      </c>
-      <c r="C254" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D254" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E254" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F254" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G254" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H254" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I254" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J254" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K254" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B255" s="16" t="inlineStr">
-        <is>
-          <t>Подготовка к проведению тренингов</t>
-        </is>
-      </c>
-      <c r="C255" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D255" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E255" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F255" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G255" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H255" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I255" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J255" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K255" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="B256" s="16" t="inlineStr">
-        <is>
-          <t>Проведение тренингов по Бережливому производству</t>
-        </is>
-      </c>
-      <c r="C256" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D256" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E256" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F256" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G256" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H256" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I256" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J256" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K256" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B257" s="16" t="inlineStr">
-        <is>
-          <t>Мониторинг проводимого обучения</t>
-        </is>
-      </c>
-      <c r="C257" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D257" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E257" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F257" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G257" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H257" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I257" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J257" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K257" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="B258" s="16" t="inlineStr">
-        <is>
-          <t>Картирование потоков и «Диаграмма спагетти»</t>
-        </is>
-      </c>
-      <c r="C258" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D258" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E258" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F258" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G258" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H258" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I258" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J258" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K258" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B259" s="16" t="inlineStr">
-        <is>
-          <t>Производственный анализ</t>
-        </is>
-      </c>
-      <c r="C259" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D259" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E259" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F259" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G259" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H259" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I259" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J259" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K259" s="17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="B260" s="16" t="inlineStr">
-        <is>
-          <t>Поток единичных изделий</t>
-        </is>
-      </c>
-      <c r="C260" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D260" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E260" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F260" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G260" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H260" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I260" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J260" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K260" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B261" s="16" t="inlineStr">
-        <is>
-          <t>Система «Канбан»</t>
-        </is>
-      </c>
-      <c r="C261" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D261" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E261" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F261" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G261" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H261" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I261" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J261" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K261" s="17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="B262" s="16" t="inlineStr">
-        <is>
-          <t>Стандартизированная работа</t>
-        </is>
-      </c>
-      <c r="C262" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D262" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E262" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F262" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G262" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H262" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I262" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J262" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K262" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="B263" s="16" t="inlineStr">
-        <is>
-          <t>Методы поиска первопричин и решения проблем</t>
-        </is>
-      </c>
-      <c r="C263" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D263" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E263" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F263" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G263" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H263" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I263" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J263" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K263" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="B264" s="16" t="inlineStr">
-        <is>
-          <t>Быстрая переналадка (SMED)</t>
-        </is>
-      </c>
-      <c r="C264" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D264" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E264" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F264" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G264" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H264" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I264" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J264" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="K264" s="17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="B265" s="16" t="inlineStr">
-        <is>
-          <t>«Poka-Yoke» (защита от ошибок)</t>
-        </is>
-      </c>
-      <c r="C265" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D265" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E265" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F265" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G265" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H265" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I265" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J265" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K265" s="17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="B266" s="16" t="inlineStr">
-        <is>
-          <t>5С на производстве и в офисе</t>
-        </is>
-      </c>
-      <c r="C266" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D266" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E266" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F266" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G266" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H266" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I266" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J266" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K266" s="17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="B267" s="16" t="inlineStr">
-        <is>
-          <t>ОЕЕ — анализ эффективности оборудования</t>
-        </is>
-      </c>
-      <c r="C267" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D267" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E267" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F267" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G267" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H267" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I267" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J267" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K267" s="17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="B268" s="16" t="inlineStr">
-        <is>
-          <t>Автономное обслуживание оборудования</t>
-        </is>
-      </c>
-      <c r="C268" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D268" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E268" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F268" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="G268" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H268" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I268" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J268" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K268" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="B269" s="16" t="inlineStr">
-        <is>
-          <t>Управление запасами</t>
-        </is>
-      </c>
-      <c r="C269" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D269" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E269" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F269" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G269" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H269" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I269" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J269" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K269" s="17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="B270" s="16" t="inlineStr">
-        <is>
-          <t>Сбор и проверка данных от предприятий-участников, выработка корректирующих мероприятий</t>
-        </is>
-      </c>
-      <c r="C270" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D270" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E270" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F270" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G270" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H270" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I270" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J270" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K270" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="B271" s="16" t="inlineStr">
-        <is>
-          <t>Мониторинг реализации программы на фазе «Тиражирование и совершенствование» (поддерживающие сессии)</t>
-        </is>
-      </c>
-      <c r="C271" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D271" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E271" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F271" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G271" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H271" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I271" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J271" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K271" s="17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="B272" s="16" t="inlineStr">
-        <is>
-          <t>Поиск и распространение лучших практик по производительности труда</t>
-        </is>
-      </c>
-      <c r="C272" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D272" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E272" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F272" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G272" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H272" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I272" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J272" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K272" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="B273" s="16" t="inlineStr">
-        <is>
-          <t>Организация работы с предложениями по улучшению (ППУ)</t>
-        </is>
-      </c>
-      <c r="C273" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D273" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E273" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F273" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G273" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H273" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I273" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="J273" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K273" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="B274" s="16" t="inlineStr">
-        <is>
-          <t>Ведение мониторинга проектов в подсистеме «Совместная работа» на ИТ-платформе</t>
-        </is>
-      </c>
-      <c r="C274" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D274" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E274" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F274" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G274" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H274" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="I274" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J274" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K274" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A159:K159"/>
     <mergeCell ref="A198:K198"/>
-    <mergeCell ref="A237:K237"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A81:K81"/>
     <mergeCell ref="A42:K42"/>
@@ -11304,7 +9939,7 @@
     <mergeCell ref="A120:K120"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:K4 C5:K5 C6:K6 C7:K7 C8:K8 C9:K9 C10:K10 C11:K11 C12:K12 C13:K13 C14:K14 C15:K15 C16:K16 C17:K17 C18:K18 C19:K19 C20:K20 C21:K21 C22:K22 C23:K23 C24:K24 C25:K25 C26:K26 C27:K27 C28:K28 C29:K29 C30:K30 C31:K31 C32:K32 C33:K33 C34:K34 C35:K35 C36:K36 C37:K37 C38:K38 C39:K39 C40:K40 C43:K43 C44:K44 C45:K45 C46:K46 C47:K47 C48:K48 C49:K49 C50:K50 C51:K51 C52:K52 C53:K53 C54:K54 C55:K55 C56:K56 C57:K57 C58:K58 C59:K59 C60:K60 C61:K61 C62:K62 C63:K63 C64:K64 C65:K65 C66:K66 C67:K67 C68:K68 C69:K69 C70:K70 C71:K71 C72:K72 C73:K73 C74:K74 C75:K75 C76:K76 C77:K77 C78:K78 C79:K79 C82:K82 C83:K83 C84:K84 C85:K85 C86:K86 C87:K87 C88:K88 C89:K89 C90:K90 C91:K91 C92:K92 C93:K93 C94:K94 C95:K95 C96:K96 C97:K97 C98:K98 C99:K99 C100:K100 C101:K101 C102:K102 C103:K103 C104:K104 C105:K105 C106:K106 C107:K107 C108:K108 C109:K109 C110:K110 C111:K111 C112:K112 C113:K113 C114:K114 C115:K115 C116:K116 C117:K117 C118:K118 C121:K121 C122:K122 C123:K123 C124:K124 C125:K125 C126:K126 C127:K127 C128:K128 C129:K129 C130:K130 C131:K131 C132:K132 C133:K133 C134:K134 C135:K135 C136:K136 C137:K137 C138:K138 C139:K139 C140:K140 C141:K141 C142:K142 C143:K143 C144:K144 C145:K145 C146:K146 C147:K147 C148:K148 C149:K149 C150:K150 C151:K151 C152:K152 C153:K153 C154:K154 C155:K155 C156:K156 C157:K157 C160:K160 C161:K161 C162:K162 C163:K163 C164:K164 C165:K165 C166:K166 C167:K167 C168:K168 C169:K169 C170:K170 C171:K171 C172:K172 C173:K173 C174:K174 C175:K175 C176:K176 C177:K177 C178:K178 C179:K179 C180:K180 C181:K181 C182:K182 C183:K183 C184:K184 C185:K185 C186:K186 C187:K187 C188:K188 C189:K189 C190:K190 C191:K191 C192:K192 C193:K193 C194:K194 C195:K195 C196:K196 C199:K199 C200:K200 C201:K201 C202:K202 C203:K203 C204:K204 C205:K205 C206:K206 C207:K207 C208:K208 C209:K209 C210:K210 C211:K211 C212:K212 C213:K213 C214:K214 C215:K215 C216:K216 C217:K217 C218:K218 C219:K219 C220:K220 C221:K221 C222:K222 C223:K223 C224:K224 C225:K225 C226:K226 C227:K227 C228:K228 C229:K229 C230:K230 C231:K231 C232:K232 C233:K233 C234:K234 C235:K235 C238:K238 C239:K239 C240:K240 C241:K241 C242:K242 C243:K243 C244:K244 C245:K245 C246:K246 C247:K247 C248:K248 C249:K249 C250:K250 C251:K251 C252:K252 C253:K253 C254:K254 C255:K255 C256:K256 C257:K257 C258:K258 C259:K259 C260:K260 C261:K261 C262:K262 C263:K263 C264:K264 C265:K265 C266:K266 C267:K267 C268:K268 C269:K269 C270:K270 C271:K271 C272:K272 C273:K273 C274:K274" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Неверная оценка" error="Введите целое число от 1 до 5" promptTitle="Шкала 1–5" prompt="Оценка 1–5 (см. шкалу на листе «Инструкция»)" type="whole" operator="between">
+    <dataValidation sqref="C4:K4 C5:K5 C6:K6 C7:K7 C8:K8 C9:K9 C10:K10 C11:K11 C12:K12 C13:K13 C14:K14 C15:K15 C16:K16 C17:K17 C18:K18 C19:K19 C20:K20 C21:K21 C22:K22 C23:K23 C24:K24 C25:K25 C26:K26 C27:K27 C28:K28 C29:K29 C30:K30 C31:K31 C32:K32 C33:K33 C34:K34 C35:K35 C36:K36 C37:K37 C38:K38 C39:K39 C40:K40 C43:K43 C44:K44 C45:K45 C46:K46 C47:K47 C48:K48 C49:K49 C50:K50 C51:K51 C52:K52 C53:K53 C54:K54 C55:K55 C56:K56 C57:K57 C58:K58 C59:K59 C60:K60 C61:K61 C62:K62 C63:K63 C64:K64 C65:K65 C66:K66 C67:K67 C68:K68 C69:K69 C70:K70 C71:K71 C72:K72 C73:K73 C74:K74 C75:K75 C76:K76 C77:K77 C78:K78 C79:K79 C82:K82 C83:K83 C84:K84 C85:K85 C86:K86 C87:K87 C88:K88 C89:K89 C90:K90 C91:K91 C92:K92 C93:K93 C94:K94 C95:K95 C96:K96 C97:K97 C98:K98 C99:K99 C100:K100 C101:K101 C102:K102 C103:K103 C104:K104 C105:K105 C106:K106 C107:K107 C108:K108 C109:K109 C110:K110 C111:K111 C112:K112 C113:K113 C114:K114 C115:K115 C116:K116 C117:K117 C118:K118 C121:K121 C122:K122 C123:K123 C124:K124 C125:K125 C126:K126 C127:K127 C128:K128 C129:K129 C130:K130 C131:K131 C132:K132 C133:K133 C134:K134 C135:K135 C136:K136 C137:K137 C138:K138 C139:K139 C140:K140 C141:K141 C142:K142 C143:K143 C144:K144 C145:K145 C146:K146 C147:K147 C148:K148 C149:K149 C150:K150 C151:K151 C152:K152 C153:K153 C154:K154 C155:K155 C156:K156 C157:K157 C160:K160 C161:K161 C162:K162 C163:K163 C164:K164 C165:K165 C166:K166 C167:K167 C168:K168 C169:K169 C170:K170 C171:K171 C172:K172 C173:K173 C174:K174 C175:K175 C176:K176 C177:K177 C178:K178 C179:K179 C180:K180 C181:K181 C182:K182 C183:K183 C184:K184 C185:K185 C186:K186 C187:K187 C188:K188 C189:K189 C190:K190 C191:K191 C192:K192 C193:K193 C194:K194 C195:K195 C196:K196 C199:K199 C200:K200 C201:K201 C202:K202 C203:K203 C204:K204 C205:K205 C206:K206 C207:K207 C208:K208 C209:K209 C210:K210 C211:K211 C212:K212 C213:K213 C214:K214 C215:K215 C216:K216 C217:K217 C218:K218 C219:K219 C220:K220 C221:K221 C222:K222 C223:K223 C224:K224 C225:K225 C226:K226 C227:K227 C228:K228 C229:K229 C230:K230 C231:K231 C232:K232 C233:K233 C234:K234 C235:K235" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Неверная оценка" error="Введите целое число от 1 до 5" promptTitle="Шкала 1–5" prompt="Оценка 1–5 (см. шкалу на листе «Инструкция»)" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -11319,7 +9954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J275"/>
+  <dimension ref="A1:J236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11403,7 +10038,7 @@
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -11447,7 +10082,7 @@
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -11491,7 +10126,7 @@
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -11535,7 +10170,7 @@
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -11579,7 +10214,7 @@
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -11623,7 +10258,7 @@
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -11667,7 +10302,7 @@
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -11711,7 +10346,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -11755,7 +10390,7 @@
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -11799,7 +10434,7 @@
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -11843,7 +10478,7 @@
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -11887,7 +10522,7 @@
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
@@ -11931,7 +10566,7 @@
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -11975,7 +10610,7 @@
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -12019,7 +10654,7 @@
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
@@ -12063,7 +10698,7 @@
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -12107,7 +10742,7 @@
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
@@ -12151,7 +10786,7 @@
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
@@ -12195,7 +10830,7 @@
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -12239,7 +10874,7 @@
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
@@ -12283,7 +10918,7 @@
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
@@ -12327,7 +10962,7 @@
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
@@ -12371,7 +11006,7 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -12415,7 +11050,7 @@
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
@@ -12459,7 +11094,7 @@
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
@@ -12503,7 +11138,7 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
@@ -12547,7 +11182,7 @@
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
@@ -12591,7 +11226,7 @@
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
@@ -12635,7 +11270,7 @@
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -12679,7 +11314,7 @@
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
@@ -12723,7 +11358,7 @@
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -12767,7 +11402,7 @@
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
@@ -12811,7 +11446,7 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
@@ -12855,7 +11490,7 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -12899,7 +11534,7 @@
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
@@ -12943,7 +11578,7 @@
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -12987,7 +11622,7 @@
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -13031,7 +11666,7 @@
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B41" s="21" t="inlineStr">
@@ -13087,7 +11722,7 @@
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -13131,7 +11766,7 @@
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -13175,7 +11810,7 @@
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -13219,7 +11854,7 @@
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -13263,7 +11898,7 @@
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -13307,7 +11942,7 @@
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
@@ -13351,7 +11986,7 @@
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -13395,7 +12030,7 @@
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -13439,7 +12074,7 @@
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -13483,7 +12118,7 @@
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -13527,7 +12162,7 @@
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -13571,7 +12206,7 @@
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -13615,7 +12250,7 @@
     <row r="55">
       <c r="A55" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -13659,7 +12294,7 @@
     <row r="56">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -13703,7 +12338,7 @@
     <row r="57">
       <c r="A57" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -13747,7 +12382,7 @@
     <row r="58">
       <c r="A58" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -13791,7 +12426,7 @@
     <row r="59">
       <c r="A59" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -13835,7 +12470,7 @@
     <row r="60">
       <c r="A60" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -13879,7 +12514,7 @@
     <row r="61">
       <c r="A61" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -13923,7 +12558,7 @@
     <row r="62">
       <c r="A62" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -13967,7 +12602,7 @@
     <row r="63">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
@@ -14011,7 +12646,7 @@
     <row r="64">
       <c r="A64" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B64" s="12" t="inlineStr">
@@ -14055,7 +12690,7 @@
     <row r="65">
       <c r="A65" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
@@ -14099,7 +12734,7 @@
     <row r="66">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B66" s="12" t="inlineStr">
@@ -14143,7 +12778,7 @@
     <row r="67">
       <c r="A67" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
@@ -14187,7 +12822,7 @@
     <row r="68">
       <c r="A68" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B68" s="12" t="inlineStr">
@@ -14231,7 +12866,7 @@
     <row r="69">
       <c r="A69" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
@@ -14275,7 +12910,7 @@
     <row r="70">
       <c r="A70" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B70" s="12" t="inlineStr">
@@ -14319,7 +12954,7 @@
     <row r="71">
       <c r="A71" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
@@ -14363,7 +12998,7 @@
     <row r="72">
       <c r="A72" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B72" s="12" t="inlineStr">
@@ -14407,7 +13042,7 @@
     <row r="73">
       <c r="A73" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
@@ -14451,7 +13086,7 @@
     <row r="74">
       <c r="A74" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B74" s="12" t="inlineStr">
@@ -14495,7 +13130,7 @@
     <row r="75">
       <c r="A75" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
@@ -14539,7 +13174,7 @@
     <row r="76">
       <c r="A76" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
@@ -14583,7 +13218,7 @@
     <row r="77">
       <c r="A77" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
@@ -14627,7 +13262,7 @@
     <row r="78">
       <c r="A78" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
@@ -14671,7 +13306,7 @@
     <row r="79">
       <c r="A79" s="19" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
@@ -14715,7 +13350,7 @@
     <row r="80">
       <c r="A80" s="21" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B80" s="21" t="inlineStr">
@@ -14771,7 +13406,7 @@
     <row r="82">
       <c r="A82" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
@@ -14815,7 +13450,7 @@
     <row r="83">
       <c r="A83" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -14859,7 +13494,7 @@
     <row r="84">
       <c r="A84" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -14903,7 +13538,7 @@
     <row r="85">
       <c r="A85" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -14947,7 +13582,7 @@
     <row r="86">
       <c r="A86" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -14991,7 +13626,7 @@
     <row r="87">
       <c r="A87" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
@@ -15035,7 +13670,7 @@
     <row r="88">
       <c r="A88" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
@@ -15079,7 +13714,7 @@
     <row r="89">
       <c r="A89" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
@@ -15123,7 +13758,7 @@
     <row r="90">
       <c r="A90" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
@@ -15167,7 +13802,7 @@
     <row r="91">
       <c r="A91" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
@@ -15211,7 +13846,7 @@
     <row r="92">
       <c r="A92" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
@@ -15255,7 +13890,7 @@
     <row r="93">
       <c r="A93" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
@@ -15299,7 +13934,7 @@
     <row r="94">
       <c r="A94" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
@@ -15343,7 +13978,7 @@
     <row r="95">
       <c r="A95" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
@@ -15387,7 +14022,7 @@
     <row r="96">
       <c r="A96" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
@@ -15431,7 +14066,7 @@
     <row r="97">
       <c r="A97" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -15475,7 +14110,7 @@
     <row r="98">
       <c r="A98" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
@@ -15519,7 +14154,7 @@
     <row r="99">
       <c r="A99" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -15563,7 +14198,7 @@
     <row r="100">
       <c r="A100" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
@@ -15607,7 +14242,7 @@
     <row r="101">
       <c r="A101" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -15651,7 +14286,7 @@
     <row r="102">
       <c r="A102" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B102" s="12" t="inlineStr">
@@ -15695,7 +14330,7 @@
     <row r="103">
       <c r="A103" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
@@ -15739,7 +14374,7 @@
     <row r="104">
       <c r="A104" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B104" s="12" t="inlineStr">
@@ -15783,7 +14418,7 @@
     <row r="105">
       <c r="A105" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
@@ -15827,7 +14462,7 @@
     <row r="106">
       <c r="A106" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B106" s="12" t="inlineStr">
@@ -15871,7 +14506,7 @@
     <row r="107">
       <c r="A107" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
@@ -15915,7 +14550,7 @@
     <row r="108">
       <c r="A108" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B108" s="12" t="inlineStr">
@@ -15959,7 +14594,7 @@
     <row r="109">
       <c r="A109" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
@@ -16003,7 +14638,7 @@
     <row r="110">
       <c r="A110" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B110" s="12" t="inlineStr">
@@ -16047,7 +14682,7 @@
     <row r="111">
       <c r="A111" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
@@ -16091,7 +14726,7 @@
     <row r="112">
       <c r="A112" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B112" s="12" t="inlineStr">
@@ -16135,7 +14770,7 @@
     <row r="113">
       <c r="A113" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
@@ -16179,7 +14814,7 @@
     <row r="114">
       <c r="A114" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
@@ -16223,7 +14858,7 @@
     <row r="115">
       <c r="A115" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
@@ -16267,7 +14902,7 @@
     <row r="116">
       <c r="A116" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
@@ -16311,7 +14946,7 @@
     <row r="117">
       <c r="A117" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
@@ -16355,7 +14990,7 @@
     <row r="118">
       <c r="A118" s="19" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
@@ -16399,7 +15034,7 @@
     <row r="119">
       <c r="A119" s="21" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B119" s="21" t="inlineStr">
@@ -16455,7 +15090,7 @@
     <row r="121">
       <c r="A121" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -16499,7 +15134,7 @@
     <row r="122">
       <c r="A122" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
@@ -16543,7 +15178,7 @@
     <row r="123">
       <c r="A123" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -16587,7 +15222,7 @@
     <row r="124">
       <c r="A124" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -16631,7 +15266,7 @@
     <row r="125">
       <c r="A125" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -16675,7 +15310,7 @@
     <row r="126">
       <c r="A126" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
@@ -16719,7 +15354,7 @@
     <row r="127">
       <c r="A127" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
@@ -16763,7 +15398,7 @@
     <row r="128">
       <c r="A128" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
@@ -16807,7 +15442,7 @@
     <row r="129">
       <c r="A129" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
@@ -16851,7 +15486,7 @@
     <row r="130">
       <c r="A130" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
@@ -16895,7 +15530,7 @@
     <row r="131">
       <c r="A131" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
@@ -16939,7 +15574,7 @@
     <row r="132">
       <c r="A132" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
@@ -16983,7 +15618,7 @@
     <row r="133">
       <c r="A133" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
@@ -17027,7 +15662,7 @@
     <row r="134">
       <c r="A134" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
@@ -17071,7 +15706,7 @@
     <row r="135">
       <c r="A135" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
@@ -17115,7 +15750,7 @@
     <row r="136">
       <c r="A136" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
@@ -17159,7 +15794,7 @@
     <row r="137">
       <c r="A137" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
@@ -17203,7 +15838,7 @@
     <row r="138">
       <c r="A138" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
@@ -17247,7 +15882,7 @@
     <row r="139">
       <c r="A139" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
@@ -17291,7 +15926,7 @@
     <row r="140">
       <c r="A140" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
@@ -17335,7 +15970,7 @@
     <row r="141">
       <c r="A141" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
@@ -17379,7 +16014,7 @@
     <row r="142">
       <c r="A142" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B142" s="12" t="inlineStr">
@@ -17423,7 +16058,7 @@
     <row r="143">
       <c r="A143" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
@@ -17467,7 +16102,7 @@
     <row r="144">
       <c r="A144" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B144" s="12" t="inlineStr">
@@ -17511,7 +16146,7 @@
     <row r="145">
       <c r="A145" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
@@ -17555,7 +16190,7 @@
     <row r="146">
       <c r="A146" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B146" s="12" t="inlineStr">
@@ -17599,7 +16234,7 @@
     <row r="147">
       <c r="A147" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
@@ -17643,7 +16278,7 @@
     <row r="148">
       <c r="A148" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B148" s="12" t="inlineStr">
@@ -17687,7 +16322,7 @@
     <row r="149">
       <c r="A149" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
@@ -17731,7 +16366,7 @@
     <row r="150">
       <c r="A150" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B150" s="12" t="inlineStr">
@@ -17775,7 +16410,7 @@
     <row r="151">
       <c r="A151" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
@@ -17819,7 +16454,7 @@
     <row r="152">
       <c r="A152" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B152" s="12" t="inlineStr">
@@ -17863,7 +16498,7 @@
     <row r="153">
       <c r="A153" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
@@ -17907,7 +16542,7 @@
     <row r="154">
       <c r="A154" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
@@ -17951,7 +16586,7 @@
     <row r="155">
       <c r="A155" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
@@ -17995,7 +16630,7 @@
     <row r="156">
       <c r="A156" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
@@ -18039,7 +16674,7 @@
     <row r="157">
       <c r="A157" s="19" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
@@ -18083,7 +16718,7 @@
     <row r="158">
       <c r="A158" s="21" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B158" s="21" t="inlineStr">
@@ -18139,7 +16774,7 @@
     <row r="160">
       <c r="A160" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -18183,7 +16818,7 @@
     <row r="161">
       <c r="A161" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -18227,7 +16862,7 @@
     <row r="162">
       <c r="A162" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -18271,7 +16906,7 @@
     <row r="163">
       <c r="A163" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -18315,7 +16950,7 @@
     <row r="164">
       <c r="A164" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -18359,7 +16994,7 @@
     <row r="165">
       <c r="A165" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
@@ -18403,7 +17038,7 @@
     <row r="166">
       <c r="A166" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
@@ -18447,7 +17082,7 @@
     <row r="167">
       <c r="A167" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
@@ -18491,7 +17126,7 @@
     <row r="168">
       <c r="A168" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
@@ -18535,7 +17170,7 @@
     <row r="169">
       <c r="A169" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
@@ -18579,7 +17214,7 @@
     <row r="170">
       <c r="A170" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
@@ -18623,7 +17258,7 @@
     <row r="171">
       <c r="A171" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
@@ -18667,7 +17302,7 @@
     <row r="172">
       <c r="A172" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
@@ -18711,7 +17346,7 @@
     <row r="173">
       <c r="A173" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
@@ -18755,7 +17390,7 @@
     <row r="174">
       <c r="A174" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
@@ -18799,7 +17434,7 @@
     <row r="175">
       <c r="A175" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
@@ -18843,7 +17478,7 @@
     <row r="176">
       <c r="A176" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
@@ -18887,7 +17522,7 @@
     <row r="177">
       <c r="A177" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
@@ -18931,7 +17566,7 @@
     <row r="178">
       <c r="A178" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B178" s="11" t="inlineStr">
@@ -18975,7 +17610,7 @@
     <row r="179">
       <c r="A179" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
@@ -19019,7 +17654,7 @@
     <row r="180">
       <c r="A180" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B180" s="12" t="inlineStr">
@@ -19063,7 +17698,7 @@
     <row r="181">
       <c r="A181" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
@@ -19107,7 +17742,7 @@
     <row r="182">
       <c r="A182" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B182" s="12" t="inlineStr">
@@ -19151,7 +17786,7 @@
     <row r="183">
       <c r="A183" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
@@ -19195,7 +17830,7 @@
     <row r="184">
       <c r="A184" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B184" s="12" t="inlineStr">
@@ -19239,7 +17874,7 @@
     <row r="185">
       <c r="A185" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
@@ -19283,7 +17918,7 @@
     <row r="186">
       <c r="A186" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B186" s="12" t="inlineStr">
@@ -19327,7 +17962,7 @@
     <row r="187">
       <c r="A187" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B187" s="12" t="inlineStr">
@@ -19371,7 +18006,7 @@
     <row r="188">
       <c r="A188" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B188" s="12" t="inlineStr">
@@ -19415,7 +18050,7 @@
     <row r="189">
       <c r="A189" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
@@ -19459,7 +18094,7 @@
     <row r="190">
       <c r="A190" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B190" s="12" t="inlineStr">
@@ -19503,7 +18138,7 @@
     <row r="191">
       <c r="A191" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B191" s="12" t="inlineStr">
@@ -19547,7 +18182,7 @@
     <row r="192">
       <c r="A192" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B192" s="13" t="inlineStr">
@@ -19591,7 +18226,7 @@
     <row r="193">
       <c r="A193" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B193" s="13" t="inlineStr">
@@ -19635,7 +18270,7 @@
     <row r="194">
       <c r="A194" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
@@ -19679,7 +18314,7 @@
     <row r="195">
       <c r="A195" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B195" s="13" t="inlineStr">
@@ -19723,7 +18358,7 @@
     <row r="196">
       <c r="A196" s="19" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B196" s="13" t="inlineStr">
@@ -19767,7 +18402,7 @@
     <row r="197">
       <c r="A197" s="21" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B197" s="21" t="inlineStr">
@@ -19823,7 +18458,7 @@
     <row r="199">
       <c r="A199" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -19867,7 +18502,7 @@
     <row r="200">
       <c r="A200" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -19911,7 +18546,7 @@
     <row r="201">
       <c r="A201" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -19955,7 +18590,7 @@
     <row r="202">
       <c r="A202" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -19999,7 +18634,7 @@
     <row r="203">
       <c r="A203" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -20043,7 +18678,7 @@
     <row r="204">
       <c r="A204" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B204" s="11" t="inlineStr">
@@ -20087,7 +18722,7 @@
     <row r="205">
       <c r="A205" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B205" s="11" t="inlineStr">
@@ -20131,7 +18766,7 @@
     <row r="206">
       <c r="A206" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B206" s="11" t="inlineStr">
@@ -20175,7 +18810,7 @@
     <row r="207">
       <c r="A207" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B207" s="11" t="inlineStr">
@@ -20219,7 +18854,7 @@
     <row r="208">
       <c r="A208" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B208" s="11" t="inlineStr">
@@ -20263,7 +18898,7 @@
     <row r="209">
       <c r="A209" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B209" s="11" t="inlineStr">
@@ -20307,7 +18942,7 @@
     <row r="210">
       <c r="A210" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B210" s="11" t="inlineStr">
@@ -20351,7 +18986,7 @@
     <row r="211">
       <c r="A211" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B211" s="11" t="inlineStr">
@@ -20395,7 +19030,7 @@
     <row r="212">
       <c r="A212" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B212" s="11" t="inlineStr">
@@ -20439,7 +19074,7 @@
     <row r="213">
       <c r="A213" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B213" s="11" t="inlineStr">
@@ -20483,7 +19118,7 @@
     <row r="214">
       <c r="A214" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B214" s="11" t="inlineStr">
@@ -20527,7 +19162,7 @@
     <row r="215">
       <c r="A215" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B215" s="11" t="inlineStr">
@@ -20571,7 +19206,7 @@
     <row r="216">
       <c r="A216" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B216" s="11" t="inlineStr">
@@ -20615,7 +19250,7 @@
     <row r="217">
       <c r="A217" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B217" s="11" t="inlineStr">
@@ -20659,7 +19294,7 @@
     <row r="218">
       <c r="A218" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B218" s="11" t="inlineStr">
@@ -20703,7 +19338,7 @@
     <row r="219">
       <c r="A219" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B219" s="12" t="inlineStr">
@@ -20747,7 +19382,7 @@
     <row r="220">
       <c r="A220" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B220" s="12" t="inlineStr">
@@ -20791,7 +19426,7 @@
     <row r="221">
       <c r="A221" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B221" s="12" t="inlineStr">
@@ -20835,7 +19470,7 @@
     <row r="222">
       <c r="A222" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B222" s="12" t="inlineStr">
@@ -20879,7 +19514,7 @@
     <row r="223">
       <c r="A223" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B223" s="12" t="inlineStr">
@@ -20923,7 +19558,7 @@
     <row r="224">
       <c r="A224" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B224" s="12" t="inlineStr">
@@ -20967,7 +19602,7 @@
     <row r="225">
       <c r="A225" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B225" s="12" t="inlineStr">
@@ -21011,7 +19646,7 @@
     <row r="226">
       <c r="A226" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B226" s="12" t="inlineStr">
@@ -21055,7 +19690,7 @@
     <row r="227">
       <c r="A227" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B227" s="12" t="inlineStr">
@@ -21099,7 +19734,7 @@
     <row r="228">
       <c r="A228" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B228" s="12" t="inlineStr">
@@ -21143,7 +19778,7 @@
     <row r="229">
       <c r="A229" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B229" s="12" t="inlineStr">
@@ -21187,7 +19822,7 @@
     <row r="230">
       <c r="A230" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B230" s="12" t="inlineStr">
@@ -21231,7 +19866,7 @@
     <row r="231">
       <c r="A231" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B231" s="13" t="inlineStr">
@@ -21275,7 +19910,7 @@
     <row r="232">
       <c r="A232" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B232" s="13" t="inlineStr">
@@ -21319,7 +19954,7 @@
     <row r="233">
       <c r="A233" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B233" s="13" t="inlineStr">
@@ -21363,7 +19998,7 @@
     <row r="234">
       <c r="A234" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B234" s="13" t="inlineStr">
@@ -21407,7 +20042,7 @@
     <row r="235">
       <c r="A235" s="19" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B235" s="13" t="inlineStr">
@@ -21451,7 +20086,7 @@
     <row r="236">
       <c r="A236" s="21" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B236" s="21" t="inlineStr">
@@ -21489,1690 +20124,6 @@
       </c>
       <c r="J236" s="21">
         <f>IF(I236="","",IF(I236&gt;=0.5,"⚠ переоценивает себя",IF(H236&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="19" t="n"/>
-      <c r="B237" s="19" t="n"/>
-      <c r="C237" s="20" t="n"/>
-      <c r="D237" s="20" t="n"/>
-      <c r="E237" s="20" t="n"/>
-      <c r="F237" s="20" t="n"/>
-      <c r="G237" s="20" t="n"/>
-      <c r="H237" s="20" t="n"/>
-      <c r="I237" s="20" t="n"/>
-      <c r="J237" s="19" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B238" s="9" t="inlineStr">
-        <is>
-          <t>Проведение оценки на соответствие предприятия обязательным критериям</t>
-        </is>
-      </c>
-      <c r="C238" s="20">
-        <f>IF('Оценки'!K238="","",'Оценки'!K238)</f>
-        <v/>
-      </c>
-      <c r="D238" s="20">
-        <f>IF('Оценки'!C238="","",'Оценки'!C238)</f>
-        <v/>
-      </c>
-      <c r="E238" s="20">
-        <f>IF(COUNT('Оценки'!D238:F238)=0,"",AVERAGE('Оценки'!D238:F238))</f>
-        <v/>
-      </c>
-      <c r="F238" s="20">
-        <f>IF(COUNT('Оценки'!G238:I238)=0,"",AVERAGE('Оценки'!G238:I238))</f>
-        <v/>
-      </c>
-      <c r="G238" s="20">
-        <f>IF('Оценки'!J238="","",'Оценки'!J238)</f>
-        <v/>
-      </c>
-      <c r="H238" s="20">
-        <f>IF(COUNT(D238:G238)=0,"",AVERAGE(D238:G238))</f>
-        <v/>
-      </c>
-      <c r="I238" s="20">
-        <f>IF(OR(C238="",H238=""),"",C238-H238)</f>
-        <v/>
-      </c>
-      <c r="J238" s="19">
-        <f>IF(I238="","",IF(I238&gt;=0.5,"⚠ переоценивает себя",IF(H238&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B239" s="9" t="inlineStr">
-        <is>
-          <t>Проведение оценки готовности руководства предприятия к участию в проекте (интервью)</t>
-        </is>
-      </c>
-      <c r="C239" s="20">
-        <f>IF('Оценки'!K239="","",'Оценки'!K239)</f>
-        <v/>
-      </c>
-      <c r="D239" s="20">
-        <f>IF('Оценки'!C239="","",'Оценки'!C239)</f>
-        <v/>
-      </c>
-      <c r="E239" s="20">
-        <f>IF(COUNT('Оценки'!D239:F239)=0,"",AVERAGE('Оценки'!D239:F239))</f>
-        <v/>
-      </c>
-      <c r="F239" s="20">
-        <f>IF(COUNT('Оценки'!G239:I239)=0,"",AVERAGE('Оценки'!G239:I239))</f>
-        <v/>
-      </c>
-      <c r="G239" s="20">
-        <f>IF('Оценки'!J239="","",'Оценки'!J239)</f>
-        <v/>
-      </c>
-      <c r="H239" s="20">
-        <f>IF(COUNT(D239:G239)=0,"",AVERAGE(D239:G239))</f>
-        <v/>
-      </c>
-      <c r="I239" s="20">
-        <f>IF(OR(C239="",H239=""),"",C239-H239)</f>
-        <v/>
-      </c>
-      <c r="J239" s="19">
-        <f>IF(I239="","",IF(I239&gt;=0.5,"⚠ переоценивает себя",IF(H239&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B240" s="9" t="inlineStr">
-        <is>
-          <t>Проведение визуальной оценки производственного процесса на предприятии (визит на площадку)</t>
-        </is>
-      </c>
-      <c r="C240" s="20">
-        <f>IF('Оценки'!K240="","",'Оценки'!K240)</f>
-        <v/>
-      </c>
-      <c r="D240" s="20">
-        <f>IF('Оценки'!C240="","",'Оценки'!C240)</f>
-        <v/>
-      </c>
-      <c r="E240" s="20">
-        <f>IF(COUNT('Оценки'!D240:F240)=0,"",AVERAGE('Оценки'!D240:F240))</f>
-        <v/>
-      </c>
-      <c r="F240" s="20">
-        <f>IF(COUNT('Оценки'!G240:I240)=0,"",AVERAGE('Оценки'!G240:I240))</f>
-        <v/>
-      </c>
-      <c r="G240" s="20">
-        <f>IF('Оценки'!J240="","",'Оценки'!J240)</f>
-        <v/>
-      </c>
-      <c r="H240" s="20">
-        <f>IF(COUNT(D240:G240)=0,"",AVERAGE(D240:G240))</f>
-        <v/>
-      </c>
-      <c r="I240" s="20">
-        <f>IF(OR(C240="",H240=""),"",C240-H240)</f>
-        <v/>
-      </c>
-      <c r="J240" s="19">
-        <f>IF(I240="","",IF(I240&gt;=0.5,"⚠ переоценивает себя",IF(H240&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B241" s="9" t="inlineStr">
-        <is>
-          <t>Вовлечение руководства предприятий в федеральный проект</t>
-        </is>
-      </c>
-      <c r="C241" s="20">
-        <f>IF('Оценки'!K241="","",'Оценки'!K241)</f>
-        <v/>
-      </c>
-      <c r="D241" s="20">
-        <f>IF('Оценки'!C241="","",'Оценки'!C241)</f>
-        <v/>
-      </c>
-      <c r="E241" s="20">
-        <f>IF(COUNT('Оценки'!D241:F241)=0,"",AVERAGE('Оценки'!D241:F241))</f>
-        <v/>
-      </c>
-      <c r="F241" s="20">
-        <f>IF(COUNT('Оценки'!G241:I241)=0,"",AVERAGE('Оценки'!G241:I241))</f>
-        <v/>
-      </c>
-      <c r="G241" s="20">
-        <f>IF('Оценки'!J241="","",'Оценки'!J241)</f>
-        <v/>
-      </c>
-      <c r="H241" s="20">
-        <f>IF(COUNT(D241:G241)=0,"",AVERAGE(D241:G241))</f>
-        <v/>
-      </c>
-      <c r="I241" s="20">
-        <f>IF(OR(C241="",H241=""),"",C241-H241)</f>
-        <v/>
-      </c>
-      <c r="J241" s="19">
-        <f>IF(I241="","",IF(I241&gt;=0.5,"⚠ переоценивает себя",IF(H241&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B242" s="9" t="inlineStr">
-        <is>
-          <t>Подписание соглашения о сотрудничестве между РЦК и предприятием</t>
-        </is>
-      </c>
-      <c r="C242" s="20">
-        <f>IF('Оценки'!K242="","",'Оценки'!K242)</f>
-        <v/>
-      </c>
-      <c r="D242" s="20">
-        <f>IF('Оценки'!C242="","",'Оценки'!C242)</f>
-        <v/>
-      </c>
-      <c r="E242" s="20">
-        <f>IF(COUNT('Оценки'!D242:F242)=0,"",AVERAGE('Оценки'!D242:F242))</f>
-        <v/>
-      </c>
-      <c r="F242" s="20">
-        <f>IF(COUNT('Оценки'!G242:I242)=0,"",AVERAGE('Оценки'!G242:I242))</f>
-        <v/>
-      </c>
-      <c r="G242" s="20">
-        <f>IF('Оценки'!J242="","",'Оценки'!J242)</f>
-        <v/>
-      </c>
-      <c r="H242" s="20">
-        <f>IF(COUNT(D242:G242)=0,"",AVERAGE(D242:G242))</f>
-        <v/>
-      </c>
-      <c r="I242" s="20">
-        <f>IF(OR(C242="",H242=""),"",C242-H242)</f>
-        <v/>
-      </c>
-      <c r="J242" s="19">
-        <f>IF(I242="","",IF(I242&gt;=0.5,"⚠ переоценивает себя",IF(H242&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B243" s="11" t="inlineStr">
-        <is>
-          <t>Реализация организационных вех программы</t>
-        </is>
-      </c>
-      <c r="C243" s="20">
-        <f>IF('Оценки'!K243="","",'Оценки'!K243)</f>
-        <v/>
-      </c>
-      <c r="D243" s="20">
-        <f>IF('Оценки'!C243="","",'Оценки'!C243)</f>
-        <v/>
-      </c>
-      <c r="E243" s="20">
-        <f>IF(COUNT('Оценки'!D243:F243)=0,"",AVERAGE('Оценки'!D243:F243))</f>
-        <v/>
-      </c>
-      <c r="F243" s="20">
-        <f>IF(COUNT('Оценки'!G243:I243)=0,"",AVERAGE('Оценки'!G243:I243))</f>
-        <v/>
-      </c>
-      <c r="G243" s="20">
-        <f>IF('Оценки'!J243="","",'Оценки'!J243)</f>
-        <v/>
-      </c>
-      <c r="H243" s="20">
-        <f>IF(COUNT(D243:G243)=0,"",AVERAGE(D243:G243))</f>
-        <v/>
-      </c>
-      <c r="I243" s="20">
-        <f>IF(OR(C243="",H243=""),"",C243-H243)</f>
-        <v/>
-      </c>
-      <c r="J243" s="19">
-        <f>IF(I243="","",IF(I243&gt;=0.5,"⚠ переоценивает себя",IF(H243&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B244" s="11" t="inlineStr">
-        <is>
-          <t>Формирование проектного офиса</t>
-        </is>
-      </c>
-      <c r="C244" s="20">
-        <f>IF('Оценки'!K244="","",'Оценки'!K244)</f>
-        <v/>
-      </c>
-      <c r="D244" s="20">
-        <f>IF('Оценки'!C244="","",'Оценки'!C244)</f>
-        <v/>
-      </c>
-      <c r="E244" s="20">
-        <f>IF(COUNT('Оценки'!D244:F244)=0,"",AVERAGE('Оценки'!D244:F244))</f>
-        <v/>
-      </c>
-      <c r="F244" s="20">
-        <f>IF(COUNT('Оценки'!G244:I244)=0,"",AVERAGE('Оценки'!G244:I244))</f>
-        <v/>
-      </c>
-      <c r="G244" s="20">
-        <f>IF('Оценки'!J244="","",'Оценки'!J244)</f>
-        <v/>
-      </c>
-      <c r="H244" s="20">
-        <f>IF(COUNT(D244:G244)=0,"",AVERAGE(D244:G244))</f>
-        <v/>
-      </c>
-      <c r="I244" s="20">
-        <f>IF(OR(C244="",H244=""),"",C244-H244)</f>
-        <v/>
-      </c>
-      <c r="J244" s="19">
-        <f>IF(I244="","",IF(I244&gt;=0.5,"⚠ переоценивает себя",IF(H244&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B245" s="11" t="inlineStr">
-        <is>
-          <t>Определение перечня вовлеченных лиц и рамок проекта; создание рабочей группы для работы с пилотным потоком</t>
-        </is>
-      </c>
-      <c r="C245" s="20">
-        <f>IF('Оценки'!K245="","",'Оценки'!K245)</f>
-        <v/>
-      </c>
-      <c r="D245" s="20">
-        <f>IF('Оценки'!C245="","",'Оценки'!C245)</f>
-        <v/>
-      </c>
-      <c r="E245" s="20">
-        <f>IF(COUNT('Оценки'!D245:F245)=0,"",AVERAGE('Оценки'!D245:F245))</f>
-        <v/>
-      </c>
-      <c r="F245" s="20">
-        <f>IF(COUNT('Оценки'!G245:I245)=0,"",AVERAGE('Оценки'!G245:I245))</f>
-        <v/>
-      </c>
-      <c r="G245" s="20">
-        <f>IF('Оценки'!J245="","",'Оценки'!J245)</f>
-        <v/>
-      </c>
-      <c r="H245" s="20">
-        <f>IF(COUNT(D245:G245)=0,"",AVERAGE(D245:G245))</f>
-        <v/>
-      </c>
-      <c r="I245" s="20">
-        <f>IF(OR(C245="",H245=""),"",C245-H245)</f>
-        <v/>
-      </c>
-      <c r="J245" s="19">
-        <f>IF(I245="","",IF(I245&gt;=0.5,"⚠ переоценивает себя",IF(H245&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B246" s="11" t="inlineStr">
-        <is>
-          <t>Выявление степени готовности предприятия к изменениям</t>
-        </is>
-      </c>
-      <c r="C246" s="20">
-        <f>IF('Оценки'!K246="","",'Оценки'!K246)</f>
-        <v/>
-      </c>
-      <c r="D246" s="20">
-        <f>IF('Оценки'!C246="","",'Оценки'!C246)</f>
-        <v/>
-      </c>
-      <c r="E246" s="20">
-        <f>IF(COUNT('Оценки'!D246:F246)=0,"",AVERAGE('Оценки'!D246:F246))</f>
-        <v/>
-      </c>
-      <c r="F246" s="20">
-        <f>IF(COUNT('Оценки'!G246:I246)=0,"",AVERAGE('Оценки'!G246:I246))</f>
-        <v/>
-      </c>
-      <c r="G246" s="20">
-        <f>IF('Оценки'!J246="","",'Оценки'!J246)</f>
-        <v/>
-      </c>
-      <c r="H246" s="20">
-        <f>IF(COUNT(D246:G246)=0,"",AVERAGE(D246:G246))</f>
-        <v/>
-      </c>
-      <c r="I246" s="20">
-        <f>IF(OR(C246="",H246=""),"",C246-H246)</f>
-        <v/>
-      </c>
-      <c r="J246" s="19">
-        <f>IF(I246="","",IF(I246&gt;=0.5,"⚠ переоценивает себя",IF(H246&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B247" s="11" t="inlineStr">
-        <is>
-          <t>Составление плана ключевых событий</t>
-        </is>
-      </c>
-      <c r="C247" s="20">
-        <f>IF('Оценки'!K247="","",'Оценки'!K247)</f>
-        <v/>
-      </c>
-      <c r="D247" s="20">
-        <f>IF('Оценки'!C247="","",'Оценки'!C247)</f>
-        <v/>
-      </c>
-      <c r="E247" s="20">
-        <f>IF(COUNT('Оценки'!D247:F247)=0,"",AVERAGE('Оценки'!D247:F247))</f>
-        <v/>
-      </c>
-      <c r="F247" s="20">
-        <f>IF(COUNT('Оценки'!G247:I247)=0,"",AVERAGE('Оценки'!G247:I247))</f>
-        <v/>
-      </c>
-      <c r="G247" s="20">
-        <f>IF('Оценки'!J247="","",'Оценки'!J247)</f>
-        <v/>
-      </c>
-      <c r="H247" s="20">
-        <f>IF(COUNT(D247:G247)=0,"",AVERAGE(D247:G247))</f>
-        <v/>
-      </c>
-      <c r="I247" s="20">
-        <f>IF(OR(C247="",H247=""),"",C247-H247)</f>
-        <v/>
-      </c>
-      <c r="J247" s="19">
-        <f>IF(I247="","",IF(I247&gt;=0.5,"⚠ переоценивает себя",IF(H247&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B248" s="11" t="inlineStr">
-        <is>
-          <t>Разработка и корректировка плана мероприятий (основные этапы, сроки, ответственные) по достижению целевого состояния</t>
-        </is>
-      </c>
-      <c r="C248" s="20">
-        <f>IF('Оценки'!K248="","",'Оценки'!K248)</f>
-        <v/>
-      </c>
-      <c r="D248" s="20">
-        <f>IF('Оценки'!C248="","",'Оценки'!C248)</f>
-        <v/>
-      </c>
-      <c r="E248" s="20">
-        <f>IF(COUNT('Оценки'!D248:F248)=0,"",AVERAGE('Оценки'!D248:F248))</f>
-        <v/>
-      </c>
-      <c r="F248" s="20">
-        <f>IF(COUNT('Оценки'!G248:I248)=0,"",AVERAGE('Оценки'!G248:I248))</f>
-        <v/>
-      </c>
-      <c r="G248" s="20">
-        <f>IF('Оценки'!J248="","",'Оценки'!J248)</f>
-        <v/>
-      </c>
-      <c r="H248" s="20">
-        <f>IF(COUNT(D248:G248)=0,"",AVERAGE(D248:G248))</f>
-        <v/>
-      </c>
-      <c r="I248" s="20">
-        <f>IF(OR(C248="",H248=""),"",C248-H248)</f>
-        <v/>
-      </c>
-      <c r="J248" s="19">
-        <f>IF(I248="","",IF(I248&gt;=0.5,"⚠ переоценивает себя",IF(H248&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B249" s="11" t="inlineStr">
-        <is>
-          <t>Проведение анализа показателей проектов повышения производительности труда</t>
-        </is>
-      </c>
-      <c r="C249" s="20">
-        <f>IF('Оценки'!K249="","",'Оценки'!K249)</f>
-        <v/>
-      </c>
-      <c r="D249" s="20">
-        <f>IF('Оценки'!C249="","",'Оценки'!C249)</f>
-        <v/>
-      </c>
-      <c r="E249" s="20">
-        <f>IF(COUNT('Оценки'!D249:F249)=0,"",AVERAGE('Оценки'!D249:F249))</f>
-        <v/>
-      </c>
-      <c r="F249" s="20">
-        <f>IF(COUNT('Оценки'!G249:I249)=0,"",AVERAGE('Оценки'!G249:I249))</f>
-        <v/>
-      </c>
-      <c r="G249" s="20">
-        <f>IF('Оценки'!J249="","",'Оценки'!J249)</f>
-        <v/>
-      </c>
-      <c r="H249" s="20">
-        <f>IF(COUNT(D249:G249)=0,"",AVERAGE(D249:G249))</f>
-        <v/>
-      </c>
-      <c r="I249" s="20">
-        <f>IF(OR(C249="",H249=""),"",C249-H249)</f>
-        <v/>
-      </c>
-      <c r="J249" s="19">
-        <f>IF(I249="","",IF(I249&gt;=0.5,"⚠ переоценивает себя",IF(H249&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B250" s="11" t="inlineStr">
-        <is>
-          <t>Создание карточки проекта</t>
-        </is>
-      </c>
-      <c r="C250" s="20">
-        <f>IF('Оценки'!K250="","",'Оценки'!K250)</f>
-        <v/>
-      </c>
-      <c r="D250" s="20">
-        <f>IF('Оценки'!C250="","",'Оценки'!C250)</f>
-        <v/>
-      </c>
-      <c r="E250" s="20">
-        <f>IF(COUNT('Оценки'!D250:F250)=0,"",AVERAGE('Оценки'!D250:F250))</f>
-        <v/>
-      </c>
-      <c r="F250" s="20">
-        <f>IF(COUNT('Оценки'!G250:I250)=0,"",AVERAGE('Оценки'!G250:I250))</f>
-        <v/>
-      </c>
-      <c r="G250" s="20">
-        <f>IF('Оценки'!J250="","",'Оценки'!J250)</f>
-        <v/>
-      </c>
-      <c r="H250" s="20">
-        <f>IF(COUNT(D250:G250)=0,"",AVERAGE(D250:G250))</f>
-        <v/>
-      </c>
-      <c r="I250" s="20">
-        <f>IF(OR(C250="",H250=""),"",C250-H250)</f>
-        <v/>
-      </c>
-      <c r="J250" s="19">
-        <f>IF(I250="","",IF(I250&gt;=0.5,"⚠ переоценивает себя",IF(H250&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B251" s="11" t="inlineStr">
-        <is>
-          <t>Создание информационного центра проекта</t>
-        </is>
-      </c>
-      <c r="C251" s="20">
-        <f>IF('Оценки'!K251="","",'Оценки'!K251)</f>
-        <v/>
-      </c>
-      <c r="D251" s="20">
-        <f>IF('Оценки'!C251="","",'Оценки'!C251)</f>
-        <v/>
-      </c>
-      <c r="E251" s="20">
-        <f>IF(COUNT('Оценки'!D251:F251)=0,"",AVERAGE('Оценки'!D251:F251))</f>
-        <v/>
-      </c>
-      <c r="F251" s="20">
-        <f>IF(COUNT('Оценки'!G251:I251)=0,"",AVERAGE('Оценки'!G251:I251))</f>
-        <v/>
-      </c>
-      <c r="G251" s="20">
-        <f>IF('Оценки'!J251="","",'Оценки'!J251)</f>
-        <v/>
-      </c>
-      <c r="H251" s="20">
-        <f>IF(COUNT(D251:G251)=0,"",AVERAGE(D251:G251))</f>
-        <v/>
-      </c>
-      <c r="I251" s="20">
-        <f>IF(OR(C251="",H251=""),"",C251-H251)</f>
-        <v/>
-      </c>
-      <c r="J251" s="19">
-        <f>IF(I251="","",IF(I251&gt;=0.5,"⚠ переоценивает себя",IF(H251&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B252" s="11" t="inlineStr">
-        <is>
-          <t>Создание эталонного участка</t>
-        </is>
-      </c>
-      <c r="C252" s="20">
-        <f>IF('Оценки'!K252="","",'Оценки'!K252)</f>
-        <v/>
-      </c>
-      <c r="D252" s="20">
-        <f>IF('Оценки'!C252="","",'Оценки'!C252)</f>
-        <v/>
-      </c>
-      <c r="E252" s="20">
-        <f>IF(COUNT('Оценки'!D252:F252)=0,"",AVERAGE('Оценки'!D252:F252))</f>
-        <v/>
-      </c>
-      <c r="F252" s="20">
-        <f>IF(COUNT('Оценки'!G252:I252)=0,"",AVERAGE('Оценки'!G252:I252))</f>
-        <v/>
-      </c>
-      <c r="G252" s="20">
-        <f>IF('Оценки'!J252="","",'Оценки'!J252)</f>
-        <v/>
-      </c>
-      <c r="H252" s="20">
-        <f>IF(COUNT(D252:G252)=0,"",AVERAGE(D252:G252))</f>
-        <v/>
-      </c>
-      <c r="I252" s="20">
-        <f>IF(OR(C252="",H252=""),"",C252-H252)</f>
-        <v/>
-      </c>
-      <c r="J252" s="19">
-        <f>IF(I252="","",IF(I252&gt;=0.5,"⚠ переоценивает себя",IF(H252&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B253" s="11" t="inlineStr">
-        <is>
-          <t>Проведение оценки уровня развития производственной системы предприятия</t>
-        </is>
-      </c>
-      <c r="C253" s="20">
-        <f>IF('Оценки'!K253="","",'Оценки'!K253)</f>
-        <v/>
-      </c>
-      <c r="D253" s="20">
-        <f>IF('Оценки'!C253="","",'Оценки'!C253)</f>
-        <v/>
-      </c>
-      <c r="E253" s="20">
-        <f>IF(COUNT('Оценки'!D253:F253)=0,"",AVERAGE('Оценки'!D253:F253))</f>
-        <v/>
-      </c>
-      <c r="F253" s="20">
-        <f>IF(COUNT('Оценки'!G253:I253)=0,"",AVERAGE('Оценки'!G253:I253))</f>
-        <v/>
-      </c>
-      <c r="G253" s="20">
-        <f>IF('Оценки'!J253="","",'Оценки'!J253)</f>
-        <v/>
-      </c>
-      <c r="H253" s="20">
-        <f>IF(COUNT(D253:G253)=0,"",AVERAGE(D253:G253))</f>
-        <v/>
-      </c>
-      <c r="I253" s="20">
-        <f>IF(OR(C253="",H253=""),"",C253-H253)</f>
-        <v/>
-      </c>
-      <c r="J253" s="19">
-        <f>IF(I253="","",IF(I253&gt;=0.5,"⚠ переоценивает себя",IF(H253&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B254" s="11" t="inlineStr">
-        <is>
-          <t>Внедрение информационных центров</t>
-        </is>
-      </c>
-      <c r="C254" s="20">
-        <f>IF('Оценки'!K254="","",'Оценки'!K254)</f>
-        <v/>
-      </c>
-      <c r="D254" s="20">
-        <f>IF('Оценки'!C254="","",'Оценки'!C254)</f>
-        <v/>
-      </c>
-      <c r="E254" s="20">
-        <f>IF(COUNT('Оценки'!D254:F254)=0,"",AVERAGE('Оценки'!D254:F254))</f>
-        <v/>
-      </c>
-      <c r="F254" s="20">
-        <f>IF(COUNT('Оценки'!G254:I254)=0,"",AVERAGE('Оценки'!G254:I254))</f>
-        <v/>
-      </c>
-      <c r="G254" s="20">
-        <f>IF('Оценки'!J254="","",'Оценки'!J254)</f>
-        <v/>
-      </c>
-      <c r="H254" s="20">
-        <f>IF(COUNT(D254:G254)=0,"",AVERAGE(D254:G254))</f>
-        <v/>
-      </c>
-      <c r="I254" s="20">
-        <f>IF(OR(C254="",H254=""),"",C254-H254)</f>
-        <v/>
-      </c>
-      <c r="J254" s="19">
-        <f>IF(I254="","",IF(I254&gt;=0.5,"⚠ переоценивает себя",IF(H254&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B255" s="11" t="inlineStr">
-        <is>
-          <t>Подготовка к проведению тренингов</t>
-        </is>
-      </c>
-      <c r="C255" s="20">
-        <f>IF('Оценки'!K255="","",'Оценки'!K255)</f>
-        <v/>
-      </c>
-      <c r="D255" s="20">
-        <f>IF('Оценки'!C255="","",'Оценки'!C255)</f>
-        <v/>
-      </c>
-      <c r="E255" s="20">
-        <f>IF(COUNT('Оценки'!D255:F255)=0,"",AVERAGE('Оценки'!D255:F255))</f>
-        <v/>
-      </c>
-      <c r="F255" s="20">
-        <f>IF(COUNT('Оценки'!G255:I255)=0,"",AVERAGE('Оценки'!G255:I255))</f>
-        <v/>
-      </c>
-      <c r="G255" s="20">
-        <f>IF('Оценки'!J255="","",'Оценки'!J255)</f>
-        <v/>
-      </c>
-      <c r="H255" s="20">
-        <f>IF(COUNT(D255:G255)=0,"",AVERAGE(D255:G255))</f>
-        <v/>
-      </c>
-      <c r="I255" s="20">
-        <f>IF(OR(C255="",H255=""),"",C255-H255)</f>
-        <v/>
-      </c>
-      <c r="J255" s="19">
-        <f>IF(I255="","",IF(I255&gt;=0.5,"⚠ переоценивает себя",IF(H255&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B256" s="11" t="inlineStr">
-        <is>
-          <t>Проведение тренингов по Бережливому производству</t>
-        </is>
-      </c>
-      <c r="C256" s="20">
-        <f>IF('Оценки'!K256="","",'Оценки'!K256)</f>
-        <v/>
-      </c>
-      <c r="D256" s="20">
-        <f>IF('Оценки'!C256="","",'Оценки'!C256)</f>
-        <v/>
-      </c>
-      <c r="E256" s="20">
-        <f>IF(COUNT('Оценки'!D256:F256)=0,"",AVERAGE('Оценки'!D256:F256))</f>
-        <v/>
-      </c>
-      <c r="F256" s="20">
-        <f>IF(COUNT('Оценки'!G256:I256)=0,"",AVERAGE('Оценки'!G256:I256))</f>
-        <v/>
-      </c>
-      <c r="G256" s="20">
-        <f>IF('Оценки'!J256="","",'Оценки'!J256)</f>
-        <v/>
-      </c>
-      <c r="H256" s="20">
-        <f>IF(COUNT(D256:G256)=0,"",AVERAGE(D256:G256))</f>
-        <v/>
-      </c>
-      <c r="I256" s="20">
-        <f>IF(OR(C256="",H256=""),"",C256-H256)</f>
-        <v/>
-      </c>
-      <c r="J256" s="19">
-        <f>IF(I256="","",IF(I256&gt;=0.5,"⚠ переоценивает себя",IF(H256&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B257" s="11" t="inlineStr">
-        <is>
-          <t>Мониторинг проводимого обучения</t>
-        </is>
-      </c>
-      <c r="C257" s="20">
-        <f>IF('Оценки'!K257="","",'Оценки'!K257)</f>
-        <v/>
-      </c>
-      <c r="D257" s="20">
-        <f>IF('Оценки'!C257="","",'Оценки'!C257)</f>
-        <v/>
-      </c>
-      <c r="E257" s="20">
-        <f>IF(COUNT('Оценки'!D257:F257)=0,"",AVERAGE('Оценки'!D257:F257))</f>
-        <v/>
-      </c>
-      <c r="F257" s="20">
-        <f>IF(COUNT('Оценки'!G257:I257)=0,"",AVERAGE('Оценки'!G257:I257))</f>
-        <v/>
-      </c>
-      <c r="G257" s="20">
-        <f>IF('Оценки'!J257="","",'Оценки'!J257)</f>
-        <v/>
-      </c>
-      <c r="H257" s="20">
-        <f>IF(COUNT(D257:G257)=0,"",AVERAGE(D257:G257))</f>
-        <v/>
-      </c>
-      <c r="I257" s="20">
-        <f>IF(OR(C257="",H257=""),"",C257-H257)</f>
-        <v/>
-      </c>
-      <c r="J257" s="19">
-        <f>IF(I257="","",IF(I257&gt;=0.5,"⚠ переоценивает себя",IF(H257&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B258" s="12" t="inlineStr">
-        <is>
-          <t>Картирование потоков и «Диаграмма спагетти»</t>
-        </is>
-      </c>
-      <c r="C258" s="20">
-        <f>IF('Оценки'!K258="","",'Оценки'!K258)</f>
-        <v/>
-      </c>
-      <c r="D258" s="20">
-        <f>IF('Оценки'!C258="","",'Оценки'!C258)</f>
-        <v/>
-      </c>
-      <c r="E258" s="20">
-        <f>IF(COUNT('Оценки'!D258:F258)=0,"",AVERAGE('Оценки'!D258:F258))</f>
-        <v/>
-      </c>
-      <c r="F258" s="20">
-        <f>IF(COUNT('Оценки'!G258:I258)=0,"",AVERAGE('Оценки'!G258:I258))</f>
-        <v/>
-      </c>
-      <c r="G258" s="20">
-        <f>IF('Оценки'!J258="","",'Оценки'!J258)</f>
-        <v/>
-      </c>
-      <c r="H258" s="20">
-        <f>IF(COUNT(D258:G258)=0,"",AVERAGE(D258:G258))</f>
-        <v/>
-      </c>
-      <c r="I258" s="20">
-        <f>IF(OR(C258="",H258=""),"",C258-H258)</f>
-        <v/>
-      </c>
-      <c r="J258" s="19">
-        <f>IF(I258="","",IF(I258&gt;=0.5,"⚠ переоценивает себя",IF(H258&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B259" s="12" t="inlineStr">
-        <is>
-          <t>Производственный анализ</t>
-        </is>
-      </c>
-      <c r="C259" s="20">
-        <f>IF('Оценки'!K259="","",'Оценки'!K259)</f>
-        <v/>
-      </c>
-      <c r="D259" s="20">
-        <f>IF('Оценки'!C259="","",'Оценки'!C259)</f>
-        <v/>
-      </c>
-      <c r="E259" s="20">
-        <f>IF(COUNT('Оценки'!D259:F259)=0,"",AVERAGE('Оценки'!D259:F259))</f>
-        <v/>
-      </c>
-      <c r="F259" s="20">
-        <f>IF(COUNT('Оценки'!G259:I259)=0,"",AVERAGE('Оценки'!G259:I259))</f>
-        <v/>
-      </c>
-      <c r="G259" s="20">
-        <f>IF('Оценки'!J259="","",'Оценки'!J259)</f>
-        <v/>
-      </c>
-      <c r="H259" s="20">
-        <f>IF(COUNT(D259:G259)=0,"",AVERAGE(D259:G259))</f>
-        <v/>
-      </c>
-      <c r="I259" s="20">
-        <f>IF(OR(C259="",H259=""),"",C259-H259)</f>
-        <v/>
-      </c>
-      <c r="J259" s="19">
-        <f>IF(I259="","",IF(I259&gt;=0.5,"⚠ переоценивает себя",IF(H259&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B260" s="12" t="inlineStr">
-        <is>
-          <t>Поток единичных изделий</t>
-        </is>
-      </c>
-      <c r="C260" s="20">
-        <f>IF('Оценки'!K260="","",'Оценки'!K260)</f>
-        <v/>
-      </c>
-      <c r="D260" s="20">
-        <f>IF('Оценки'!C260="","",'Оценки'!C260)</f>
-        <v/>
-      </c>
-      <c r="E260" s="20">
-        <f>IF(COUNT('Оценки'!D260:F260)=0,"",AVERAGE('Оценки'!D260:F260))</f>
-        <v/>
-      </c>
-      <c r="F260" s="20">
-        <f>IF(COUNT('Оценки'!G260:I260)=0,"",AVERAGE('Оценки'!G260:I260))</f>
-        <v/>
-      </c>
-      <c r="G260" s="20">
-        <f>IF('Оценки'!J260="","",'Оценки'!J260)</f>
-        <v/>
-      </c>
-      <c r="H260" s="20">
-        <f>IF(COUNT(D260:G260)=0,"",AVERAGE(D260:G260))</f>
-        <v/>
-      </c>
-      <c r="I260" s="20">
-        <f>IF(OR(C260="",H260=""),"",C260-H260)</f>
-        <v/>
-      </c>
-      <c r="J260" s="19">
-        <f>IF(I260="","",IF(I260&gt;=0.5,"⚠ переоценивает себя",IF(H260&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B261" s="12" t="inlineStr">
-        <is>
-          <t>Система «Канбан»</t>
-        </is>
-      </c>
-      <c r="C261" s="20">
-        <f>IF('Оценки'!K261="","",'Оценки'!K261)</f>
-        <v/>
-      </c>
-      <c r="D261" s="20">
-        <f>IF('Оценки'!C261="","",'Оценки'!C261)</f>
-        <v/>
-      </c>
-      <c r="E261" s="20">
-        <f>IF(COUNT('Оценки'!D261:F261)=0,"",AVERAGE('Оценки'!D261:F261))</f>
-        <v/>
-      </c>
-      <c r="F261" s="20">
-        <f>IF(COUNT('Оценки'!G261:I261)=0,"",AVERAGE('Оценки'!G261:I261))</f>
-        <v/>
-      </c>
-      <c r="G261" s="20">
-        <f>IF('Оценки'!J261="","",'Оценки'!J261)</f>
-        <v/>
-      </c>
-      <c r="H261" s="20">
-        <f>IF(COUNT(D261:G261)=0,"",AVERAGE(D261:G261))</f>
-        <v/>
-      </c>
-      <c r="I261" s="20">
-        <f>IF(OR(C261="",H261=""),"",C261-H261)</f>
-        <v/>
-      </c>
-      <c r="J261" s="19">
-        <f>IF(I261="","",IF(I261&gt;=0.5,"⚠ переоценивает себя",IF(H261&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B262" s="12" t="inlineStr">
-        <is>
-          <t>Стандартизированная работа</t>
-        </is>
-      </c>
-      <c r="C262" s="20">
-        <f>IF('Оценки'!K262="","",'Оценки'!K262)</f>
-        <v/>
-      </c>
-      <c r="D262" s="20">
-        <f>IF('Оценки'!C262="","",'Оценки'!C262)</f>
-        <v/>
-      </c>
-      <c r="E262" s="20">
-        <f>IF(COUNT('Оценки'!D262:F262)=0,"",AVERAGE('Оценки'!D262:F262))</f>
-        <v/>
-      </c>
-      <c r="F262" s="20">
-        <f>IF(COUNT('Оценки'!G262:I262)=0,"",AVERAGE('Оценки'!G262:I262))</f>
-        <v/>
-      </c>
-      <c r="G262" s="20">
-        <f>IF('Оценки'!J262="","",'Оценки'!J262)</f>
-        <v/>
-      </c>
-      <c r="H262" s="20">
-        <f>IF(COUNT(D262:G262)=0,"",AVERAGE(D262:G262))</f>
-        <v/>
-      </c>
-      <c r="I262" s="20">
-        <f>IF(OR(C262="",H262=""),"",C262-H262)</f>
-        <v/>
-      </c>
-      <c r="J262" s="19">
-        <f>IF(I262="","",IF(I262&gt;=0.5,"⚠ переоценивает себя",IF(H262&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B263" s="12" t="inlineStr">
-        <is>
-          <t>Методы поиска первопричин и решения проблем</t>
-        </is>
-      </c>
-      <c r="C263" s="20">
-        <f>IF('Оценки'!K263="","",'Оценки'!K263)</f>
-        <v/>
-      </c>
-      <c r="D263" s="20">
-        <f>IF('Оценки'!C263="","",'Оценки'!C263)</f>
-        <v/>
-      </c>
-      <c r="E263" s="20">
-        <f>IF(COUNT('Оценки'!D263:F263)=0,"",AVERAGE('Оценки'!D263:F263))</f>
-        <v/>
-      </c>
-      <c r="F263" s="20">
-        <f>IF(COUNT('Оценки'!G263:I263)=0,"",AVERAGE('Оценки'!G263:I263))</f>
-        <v/>
-      </c>
-      <c r="G263" s="20">
-        <f>IF('Оценки'!J263="","",'Оценки'!J263)</f>
-        <v/>
-      </c>
-      <c r="H263" s="20">
-        <f>IF(COUNT(D263:G263)=0,"",AVERAGE(D263:G263))</f>
-        <v/>
-      </c>
-      <c r="I263" s="20">
-        <f>IF(OR(C263="",H263=""),"",C263-H263)</f>
-        <v/>
-      </c>
-      <c r="J263" s="19">
-        <f>IF(I263="","",IF(I263&gt;=0.5,"⚠ переоценивает себя",IF(H263&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B264" s="12" t="inlineStr">
-        <is>
-          <t>Быстрая переналадка (SMED)</t>
-        </is>
-      </c>
-      <c r="C264" s="20">
-        <f>IF('Оценки'!K264="","",'Оценки'!K264)</f>
-        <v/>
-      </c>
-      <c r="D264" s="20">
-        <f>IF('Оценки'!C264="","",'Оценки'!C264)</f>
-        <v/>
-      </c>
-      <c r="E264" s="20">
-        <f>IF(COUNT('Оценки'!D264:F264)=0,"",AVERAGE('Оценки'!D264:F264))</f>
-        <v/>
-      </c>
-      <c r="F264" s="20">
-        <f>IF(COUNT('Оценки'!G264:I264)=0,"",AVERAGE('Оценки'!G264:I264))</f>
-        <v/>
-      </c>
-      <c r="G264" s="20">
-        <f>IF('Оценки'!J264="","",'Оценки'!J264)</f>
-        <v/>
-      </c>
-      <c r="H264" s="20">
-        <f>IF(COUNT(D264:G264)=0,"",AVERAGE(D264:G264))</f>
-        <v/>
-      </c>
-      <c r="I264" s="20">
-        <f>IF(OR(C264="",H264=""),"",C264-H264)</f>
-        <v/>
-      </c>
-      <c r="J264" s="19">
-        <f>IF(I264="","",IF(I264&gt;=0.5,"⚠ переоценивает себя",IF(H264&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B265" s="12" t="inlineStr">
-        <is>
-          <t>«Poka-Yoke» (защита от ошибок)</t>
-        </is>
-      </c>
-      <c r="C265" s="20">
-        <f>IF('Оценки'!K265="","",'Оценки'!K265)</f>
-        <v/>
-      </c>
-      <c r="D265" s="20">
-        <f>IF('Оценки'!C265="","",'Оценки'!C265)</f>
-        <v/>
-      </c>
-      <c r="E265" s="20">
-        <f>IF(COUNT('Оценки'!D265:F265)=0,"",AVERAGE('Оценки'!D265:F265))</f>
-        <v/>
-      </c>
-      <c r="F265" s="20">
-        <f>IF(COUNT('Оценки'!G265:I265)=0,"",AVERAGE('Оценки'!G265:I265))</f>
-        <v/>
-      </c>
-      <c r="G265" s="20">
-        <f>IF('Оценки'!J265="","",'Оценки'!J265)</f>
-        <v/>
-      </c>
-      <c r="H265" s="20">
-        <f>IF(COUNT(D265:G265)=0,"",AVERAGE(D265:G265))</f>
-        <v/>
-      </c>
-      <c r="I265" s="20">
-        <f>IF(OR(C265="",H265=""),"",C265-H265)</f>
-        <v/>
-      </c>
-      <c r="J265" s="19">
-        <f>IF(I265="","",IF(I265&gt;=0.5,"⚠ переоценивает себя",IF(H265&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B266" s="12" t="inlineStr">
-        <is>
-          <t>5С на производстве и в офисе</t>
-        </is>
-      </c>
-      <c r="C266" s="20">
-        <f>IF('Оценки'!K266="","",'Оценки'!K266)</f>
-        <v/>
-      </c>
-      <c r="D266" s="20">
-        <f>IF('Оценки'!C266="","",'Оценки'!C266)</f>
-        <v/>
-      </c>
-      <c r="E266" s="20">
-        <f>IF(COUNT('Оценки'!D266:F266)=0,"",AVERAGE('Оценки'!D266:F266))</f>
-        <v/>
-      </c>
-      <c r="F266" s="20">
-        <f>IF(COUNT('Оценки'!G266:I266)=0,"",AVERAGE('Оценки'!G266:I266))</f>
-        <v/>
-      </c>
-      <c r="G266" s="20">
-        <f>IF('Оценки'!J266="","",'Оценки'!J266)</f>
-        <v/>
-      </c>
-      <c r="H266" s="20">
-        <f>IF(COUNT(D266:G266)=0,"",AVERAGE(D266:G266))</f>
-        <v/>
-      </c>
-      <c r="I266" s="20">
-        <f>IF(OR(C266="",H266=""),"",C266-H266)</f>
-        <v/>
-      </c>
-      <c r="J266" s="19">
-        <f>IF(I266="","",IF(I266&gt;=0.5,"⚠ переоценивает себя",IF(H266&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B267" s="12" t="inlineStr">
-        <is>
-          <t>ОЕЕ — анализ эффективности оборудования</t>
-        </is>
-      </c>
-      <c r="C267" s="20">
-        <f>IF('Оценки'!K267="","",'Оценки'!K267)</f>
-        <v/>
-      </c>
-      <c r="D267" s="20">
-        <f>IF('Оценки'!C267="","",'Оценки'!C267)</f>
-        <v/>
-      </c>
-      <c r="E267" s="20">
-        <f>IF(COUNT('Оценки'!D267:F267)=0,"",AVERAGE('Оценки'!D267:F267))</f>
-        <v/>
-      </c>
-      <c r="F267" s="20">
-        <f>IF(COUNT('Оценки'!G267:I267)=0,"",AVERAGE('Оценки'!G267:I267))</f>
-        <v/>
-      </c>
-      <c r="G267" s="20">
-        <f>IF('Оценки'!J267="","",'Оценки'!J267)</f>
-        <v/>
-      </c>
-      <c r="H267" s="20">
-        <f>IF(COUNT(D267:G267)=0,"",AVERAGE(D267:G267))</f>
-        <v/>
-      </c>
-      <c r="I267" s="20">
-        <f>IF(OR(C267="",H267=""),"",C267-H267)</f>
-        <v/>
-      </c>
-      <c r="J267" s="19">
-        <f>IF(I267="","",IF(I267&gt;=0.5,"⚠ переоценивает себя",IF(H267&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B268" s="12" t="inlineStr">
-        <is>
-          <t>Автономное обслуживание оборудования</t>
-        </is>
-      </c>
-      <c r="C268" s="20">
-        <f>IF('Оценки'!K268="","",'Оценки'!K268)</f>
-        <v/>
-      </c>
-      <c r="D268" s="20">
-        <f>IF('Оценки'!C268="","",'Оценки'!C268)</f>
-        <v/>
-      </c>
-      <c r="E268" s="20">
-        <f>IF(COUNT('Оценки'!D268:F268)=0,"",AVERAGE('Оценки'!D268:F268))</f>
-        <v/>
-      </c>
-      <c r="F268" s="20">
-        <f>IF(COUNT('Оценки'!G268:I268)=0,"",AVERAGE('Оценки'!G268:I268))</f>
-        <v/>
-      </c>
-      <c r="G268" s="20">
-        <f>IF('Оценки'!J268="","",'Оценки'!J268)</f>
-        <v/>
-      </c>
-      <c r="H268" s="20">
-        <f>IF(COUNT(D268:G268)=0,"",AVERAGE(D268:G268))</f>
-        <v/>
-      </c>
-      <c r="I268" s="20">
-        <f>IF(OR(C268="",H268=""),"",C268-H268)</f>
-        <v/>
-      </c>
-      <c r="J268" s="19">
-        <f>IF(I268="","",IF(I268&gt;=0.5,"⚠ переоценивает себя",IF(H268&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B269" s="12" t="inlineStr">
-        <is>
-          <t>Управление запасами</t>
-        </is>
-      </c>
-      <c r="C269" s="20">
-        <f>IF('Оценки'!K269="","",'Оценки'!K269)</f>
-        <v/>
-      </c>
-      <c r="D269" s="20">
-        <f>IF('Оценки'!C269="","",'Оценки'!C269)</f>
-        <v/>
-      </c>
-      <c r="E269" s="20">
-        <f>IF(COUNT('Оценки'!D269:F269)=0,"",AVERAGE('Оценки'!D269:F269))</f>
-        <v/>
-      </c>
-      <c r="F269" s="20">
-        <f>IF(COUNT('Оценки'!G269:I269)=0,"",AVERAGE('Оценки'!G269:I269))</f>
-        <v/>
-      </c>
-      <c r="G269" s="20">
-        <f>IF('Оценки'!J269="","",'Оценки'!J269)</f>
-        <v/>
-      </c>
-      <c r="H269" s="20">
-        <f>IF(COUNT(D269:G269)=0,"",AVERAGE(D269:G269))</f>
-        <v/>
-      </c>
-      <c r="I269" s="20">
-        <f>IF(OR(C269="",H269=""),"",C269-H269)</f>
-        <v/>
-      </c>
-      <c r="J269" s="19">
-        <f>IF(I269="","",IF(I269&gt;=0.5,"⚠ переоценивает себя",IF(H269&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B270" s="13" t="inlineStr">
-        <is>
-          <t>Сбор и проверка данных от предприятий-участников, выработка корректирующих мероприятий</t>
-        </is>
-      </c>
-      <c r="C270" s="20">
-        <f>IF('Оценки'!K270="","",'Оценки'!K270)</f>
-        <v/>
-      </c>
-      <c r="D270" s="20">
-        <f>IF('Оценки'!C270="","",'Оценки'!C270)</f>
-        <v/>
-      </c>
-      <c r="E270" s="20">
-        <f>IF(COUNT('Оценки'!D270:F270)=0,"",AVERAGE('Оценки'!D270:F270))</f>
-        <v/>
-      </c>
-      <c r="F270" s="20">
-        <f>IF(COUNT('Оценки'!G270:I270)=0,"",AVERAGE('Оценки'!G270:I270))</f>
-        <v/>
-      </c>
-      <c r="G270" s="20">
-        <f>IF('Оценки'!J270="","",'Оценки'!J270)</f>
-        <v/>
-      </c>
-      <c r="H270" s="20">
-        <f>IF(COUNT(D270:G270)=0,"",AVERAGE(D270:G270))</f>
-        <v/>
-      </c>
-      <c r="I270" s="20">
-        <f>IF(OR(C270="",H270=""),"",C270-H270)</f>
-        <v/>
-      </c>
-      <c r="J270" s="19">
-        <f>IF(I270="","",IF(I270&gt;=0.5,"⚠ переоценивает себя",IF(H270&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B271" s="13" t="inlineStr">
-        <is>
-          <t>Мониторинг реализации программы на фазе «Тиражирование и совершенствование» (поддерживающие сессии)</t>
-        </is>
-      </c>
-      <c r="C271" s="20">
-        <f>IF('Оценки'!K271="","",'Оценки'!K271)</f>
-        <v/>
-      </c>
-      <c r="D271" s="20">
-        <f>IF('Оценки'!C271="","",'Оценки'!C271)</f>
-        <v/>
-      </c>
-      <c r="E271" s="20">
-        <f>IF(COUNT('Оценки'!D271:F271)=0,"",AVERAGE('Оценки'!D271:F271))</f>
-        <v/>
-      </c>
-      <c r="F271" s="20">
-        <f>IF(COUNT('Оценки'!G271:I271)=0,"",AVERAGE('Оценки'!G271:I271))</f>
-        <v/>
-      </c>
-      <c r="G271" s="20">
-        <f>IF('Оценки'!J271="","",'Оценки'!J271)</f>
-        <v/>
-      </c>
-      <c r="H271" s="20">
-        <f>IF(COUNT(D271:G271)=0,"",AVERAGE(D271:G271))</f>
-        <v/>
-      </c>
-      <c r="I271" s="20">
-        <f>IF(OR(C271="",H271=""),"",C271-H271)</f>
-        <v/>
-      </c>
-      <c r="J271" s="19">
-        <f>IF(I271="","",IF(I271&gt;=0.5,"⚠ переоценивает себя",IF(H271&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B272" s="13" t="inlineStr">
-        <is>
-          <t>Поиск и распространение лучших практик по производительности труда</t>
-        </is>
-      </c>
-      <c r="C272" s="20">
-        <f>IF('Оценки'!K272="","",'Оценки'!K272)</f>
-        <v/>
-      </c>
-      <c r="D272" s="20">
-        <f>IF('Оценки'!C272="","",'Оценки'!C272)</f>
-        <v/>
-      </c>
-      <c r="E272" s="20">
-        <f>IF(COUNT('Оценки'!D272:F272)=0,"",AVERAGE('Оценки'!D272:F272))</f>
-        <v/>
-      </c>
-      <c r="F272" s="20">
-        <f>IF(COUNT('Оценки'!G272:I272)=0,"",AVERAGE('Оценки'!G272:I272))</f>
-        <v/>
-      </c>
-      <c r="G272" s="20">
-        <f>IF('Оценки'!J272="","",'Оценки'!J272)</f>
-        <v/>
-      </c>
-      <c r="H272" s="20">
-        <f>IF(COUNT(D272:G272)=0,"",AVERAGE(D272:G272))</f>
-        <v/>
-      </c>
-      <c r="I272" s="20">
-        <f>IF(OR(C272="",H272=""),"",C272-H272)</f>
-        <v/>
-      </c>
-      <c r="J272" s="19">
-        <f>IF(I272="","",IF(I272&gt;=0.5,"⚠ переоценивает себя",IF(H272&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B273" s="13" t="inlineStr">
-        <is>
-          <t>Организация работы с предложениями по улучшению (ППУ)</t>
-        </is>
-      </c>
-      <c r="C273" s="20">
-        <f>IF('Оценки'!K273="","",'Оценки'!K273)</f>
-        <v/>
-      </c>
-      <c r="D273" s="20">
-        <f>IF('Оценки'!C273="","",'Оценки'!C273)</f>
-        <v/>
-      </c>
-      <c r="E273" s="20">
-        <f>IF(COUNT('Оценки'!D273:F273)=0,"",AVERAGE('Оценки'!D273:F273))</f>
-        <v/>
-      </c>
-      <c r="F273" s="20">
-        <f>IF(COUNT('Оценки'!G273:I273)=0,"",AVERAGE('Оценки'!G273:I273))</f>
-        <v/>
-      </c>
-      <c r="G273" s="20">
-        <f>IF('Оценки'!J273="","",'Оценки'!J273)</f>
-        <v/>
-      </c>
-      <c r="H273" s="20">
-        <f>IF(COUNT(D273:G273)=0,"",AVERAGE(D273:G273))</f>
-        <v/>
-      </c>
-      <c r="I273" s="20">
-        <f>IF(OR(C273="",H273=""),"",C273-H273)</f>
-        <v/>
-      </c>
-      <c r="J273" s="19">
-        <f>IF(I273="","",IF(I273&gt;=0.5,"⚠ переоценивает себя",IF(H273&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="19" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B274" s="13" t="inlineStr">
-        <is>
-          <t>Ведение мониторинга проектов в подсистеме «Совместная работа» на ИТ-платформе</t>
-        </is>
-      </c>
-      <c r="C274" s="20">
-        <f>IF('Оценки'!K274="","",'Оценки'!K274)</f>
-        <v/>
-      </c>
-      <c r="D274" s="20">
-        <f>IF('Оценки'!C274="","",'Оценки'!C274)</f>
-        <v/>
-      </c>
-      <c r="E274" s="20">
-        <f>IF(COUNT('Оценки'!D274:F274)=0,"",AVERAGE('Оценки'!D274:F274))</f>
-        <v/>
-      </c>
-      <c r="F274" s="20">
-        <f>IF(COUNT('Оценки'!G274:I274)=0,"",AVERAGE('Оценки'!G274:I274))</f>
-        <v/>
-      </c>
-      <c r="G274" s="20">
-        <f>IF('Оценки'!J274="","",'Оценки'!J274)</f>
-        <v/>
-      </c>
-      <c r="H274" s="20">
-        <f>IF(COUNT(D274:G274)=0,"",AVERAGE(D274:G274))</f>
-        <v/>
-      </c>
-      <c r="I274" s="20">
-        <f>IF(OR(C274="",H274=""),"",C274-H274)</f>
-        <v/>
-      </c>
-      <c r="J274" s="19">
-        <f>IF(I274="","",IF(I274&gt;=0.5,"⚠ переоценивает себя",IF(H274&lt;3,"низкий уровень","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="21" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B275" s="21" t="inlineStr">
-        <is>
-          <t>ИТОГО (среднее по всем компетенциям)</t>
-        </is>
-      </c>
-      <c r="C275" s="22">
-        <f>IF(COUNT(C238:C274)=0,"",AVERAGE(C238:C274))</f>
-        <v/>
-      </c>
-      <c r="D275" s="22">
-        <f>IF(COUNT(D238:D274)=0,"",AVERAGE(D238:D274))</f>
-        <v/>
-      </c>
-      <c r="E275" s="22">
-        <f>IF(COUNT(E238:E274)=0,"",AVERAGE(E238:E274))</f>
-        <v/>
-      </c>
-      <c r="F275" s="22">
-        <f>IF(COUNT(F238:F274)=0,"",AVERAGE(F238:F274))</f>
-        <v/>
-      </c>
-      <c r="G275" s="22">
-        <f>IF(COUNT(G238:G274)=0,"",AVERAGE(G238:G274))</f>
-        <v/>
-      </c>
-      <c r="H275" s="22">
-        <f>IF(COUNT(H238:H274)=0,"",AVERAGE(H238:H274))</f>
-        <v/>
-      </c>
-      <c r="I275" s="22">
-        <f>IF(OR(C275="",H275=""),"",C275-H275)</f>
-        <v/>
-      </c>
-      <c r="J275" s="21">
-        <f>IF(I275="","",IF(I275&gt;=0.5,"⚠ переоценивает себя",IF(H275&lt;3,"низкий уровень","")))</f>
         <v/>
       </c>
     </row>
@@ -23181,12 +20132,12 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I4:I275">
+  <conditionalFormatting sqref="I4:I236">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H275">
+  <conditionalFormatting sqref="H4:H236">
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
       <formula>3</formula>
     </cfRule>
@@ -23201,7 +20152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -23303,7 +20254,7 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B4" s="20">
@@ -23358,7 +20309,7 @@
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>РП-2 — Петров И. С. (ДЕМО)</t>
+          <t>РП-2 — Горбунова А. М. (ДЕМО)</t>
         </is>
       </c>
       <c r="B5" s="20">
@@ -23413,7 +20364,7 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
-          <t>РП-3 — Кузнецова Е. В. (ДЕМО)</t>
+          <t>РП-3 — Бутым Б. С. (ДЕМО)</t>
         </is>
       </c>
       <c r="B6" s="20">
@@ -23468,7 +20419,7 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>РП-4 — Волков Д. А. (ДЕМО)</t>
+          <t>РП-4 — Маслаков А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B7" s="20">
@@ -23523,7 +20474,7 @@
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B8" s="20">
@@ -23578,7 +20529,7 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>РП-6 — Морозов К. Л. (ДЕМО)</t>
+          <t>РП-6 — Неробеева А. Э. (ДЕМО)</t>
         </is>
       </c>
       <c r="B9" s="20">
@@ -23627,61 +20578,6 @@
       </c>
       <c r="M9" s="10">
         <f>IF('Сводка'!H236="","ожидают данные",IF('Сводка'!I236&gt;=0.7,"есть слепые зоны — обсудить с руководителем; развитие: зоны из колонок I–J",IF(AND('Сводка'!H236&gt;=3.7,ABS('Сводка'!I236)&lt;0.4),"устойчиво высокий уровень, сильная сторона команды",IF('Сводка'!H236&lt;3,"ниже требуемого уровня — план развития по зонам I–J","в целом соответствует требованиям"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>РП-7 — Васильев Т. Р. (ДЕМО)</t>
-        </is>
-      </c>
-      <c r="B10" s="20">
-        <f>IF('Сводка'!C275="","",'Сводка'!C275)</f>
-        <v/>
-      </c>
-      <c r="C10" s="20">
-        <f>IF('Сводка'!H275="","",'Сводка'!H275)</f>
-        <v/>
-      </c>
-      <c r="D10" s="20">
-        <f>IF('Сводка'!I275="","",'Сводка'!I275)</f>
-        <v/>
-      </c>
-      <c r="E10" s="20">
-        <f>IF(COUNT('Сводка'!H238:H242)=0,"",AVERAGE('Сводка'!H238:H242))</f>
-        <v/>
-      </c>
-      <c r="F10" s="20">
-        <f>IF(COUNT('Сводка'!H243:H257)=0,"",AVERAGE('Сводка'!H243:H257))</f>
-        <v/>
-      </c>
-      <c r="G10" s="20">
-        <f>IF(COUNT('Сводка'!H258:H269)=0,"",AVERAGE('Сводка'!H258:H269))</f>
-        <v/>
-      </c>
-      <c r="H10" s="20">
-        <f>IF(COUNT('Сводка'!H270:H274)=0,"",AVERAGE('Сводка'!H270:H274))</f>
-        <v/>
-      </c>
-      <c r="I10" s="10">
-        <f>IF(COUNT('Сводка'!$H$238:$H$274)&lt;2,"",INDEX('Сводка'!$B$238:$B$274,MATCH(LARGE('Сводка'!$H$238:$H$274,1),'Сводка'!$H$238:$H$274,0)))</f>
-        <v/>
-      </c>
-      <c r="J10" s="10">
-        <f>IF(COUNT('Сводка'!$H$238:$H$274)&lt;3,"",INDEX('Сводка'!$B$238:$B$274,MATCH(LARGE('Сводка'!$H$238:$H$274,2),'Сводка'!$H$238:$H$274,0)))</f>
-        <v/>
-      </c>
-      <c r="K10" s="10">
-        <f>IF(COUNT('Сводка'!$H$238:$H$274)&lt;2,"",INDEX('Сводка'!$B$238:$B$274,MATCH(MIN('Сводка'!$H$238:$H$274),'Сводка'!$H$238:$H$274,0)))</f>
-        <v/>
-      </c>
-      <c r="L10" s="10">
-        <f>IF(COUNT('Сводка'!$H$238:$H$274)&lt;3,"",INDEX('Сводка'!$B$238:$B$274,MATCH(LARGE('Сводка'!$H$238:$H$274,COUNT('Сводка'!$H$238:$H$274)-1),'Сводка'!$H$238:$H$274,0)))</f>
-        <v/>
-      </c>
-      <c r="M10" s="10">
-        <f>IF('Сводка'!H275="","ожидают данные",IF('Сводка'!I275&gt;=0.7,"есть слепые зоны — обсудить с руководителем; развитие: зоны из колонок I–J",IF(AND('Сводка'!H275&gt;=3.7,ABS('Сводка'!I275)&lt;0.4),"устойчиво высокий уровень, сильная сторона команды",IF('Сводка'!H275&lt;3,"ниже требуемого уровня — план развития по зонам I–J","в целом соответствует требованиям"))))</f>
         <v/>
       </c>
     </row>
@@ -23690,32 +20586,32 @@
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D10">
+  <conditionalFormatting sqref="D4:D9">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C10">
+  <conditionalFormatting sqref="C4:C9">
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E10">
+  <conditionalFormatting sqref="E4:E9">
     <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="1">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F10">
+  <conditionalFormatting sqref="F4:F9">
     <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G10">
+  <conditionalFormatting sqref="G4:G9">
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="1">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
+  <conditionalFormatting sqref="H4:H9">
     <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
       <formula>3</formula>
     </cfRule>
@@ -23814,7 +20710,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>РП-1 — Смирнов А. П. (ДЕМО)</t>
+          <t>РП-1 — Кущенко Д. А. (ДЕМО)</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
@@ -23862,7 +20758,7 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>РП-5 — Соколова М. Н. (ДЕМО)</t>
+          <t>РП-5 — Яковлев А. В. (ДЕМО)</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
